--- a/deliverables/VRP_GL_rollforward.xlsx
+++ b/deliverables/VRP_GL_rollforward.xlsx
@@ -9,11 +9,12 @@
   </bookViews>
   <sheets>
     <sheet name="요약" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="분개상세" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="VRP 지급내역" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="회사자료 대사" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="분개상세" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="VRP 지급내역" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">분개상세!$A$1:$N$101</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">분개상세!$A$1:$N$101</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="871" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="917" uniqueCount="163">
   <si>
     <t xml:space="preserve">VRP 구조조정충당부채 GL 정리 (2026.01~09)</t>
   </si>
@@ -183,7 +184,7 @@
     <t xml:space="preserve">5. GL 확인 결과 및 검토 포인트</t>
   </si>
   <si>
-    <t xml:space="preserve">① 38160000 9월말 잔액 4,473,184,387원 = '25 Drive 2 잔액 3,513,650,452원 + '26 신규 4건 959,533,935원(Key market 386.2 / Argos 36.9 / Procurement 290.8 / DD&amp;O 245.6백만원). BSPL과 일치.</t>
+    <t xml:space="preserve">① 38160000 9월말 잔액 4,473,184,387원 = '25 Drive 2 잔액 3,513,646,441원 + '26 신규 4건 959,537,946원(Key market 386.2 / Argos 36.9 / Procurement 290.8 / DD&amp;O 245.6백만원). BSPL과 일치.</t>
   </si>
   <si>
     <t xml:space="preserve">② '25 Drive 2: 기초 16,873.6백만원 → 사용 11,088.6백만원(1월 9,029.9 / 2월 763.8 / 4월 552.4 / 7월 742.5), 3월 환입 2,271.4백만원, 9월말 잔액 3,513.7백만원. 전기말 설정액의 13.5%를 환입했고, 9개월 경과 후에도 20.8%가 미지급 → 대상자별 지급예정표 확인 필요.</t>
@@ -207,7 +208,112 @@
     <t xml:space="preserve">⑧ 42910311 전직지원: 기초 122.5백만원 → 9월말 42.0백만원. 68063200(지급수수료-Outplacement) YTD 10.5백만원은 충당부채와 상계되지 않은 비용 → 이중 인식 여부 확인.</t>
   </si>
   <si>
-    <t xml:space="preserve">⑨ 회사 VRP 정리자료(4.06_VRP_2026.xlsx)는 암호화(민감도 레이블/비밀번호)되어 열 수 없어 대사 미완료 → 암호 해제본 수령 후 본 시트 1~4와 대사 예정.</t>
+    <t xml:space="preserve">⑨ 회사 VRP 자료(4.06_VRP_2026, Simulation Template) 대사: 2026년 퇴직 6건 중 금액 기재 4건 2,712.6백만원. 4월 552.4·7월 742.5백만원은 GL 사용액과 일치, 1월말 퇴직 776.7백만원은 2월 사용 773.2백만원과 3.5백만원 차이(전직지원 3.5백만원 포함 추정). 2월 전표에는 1월 과다 사용 조정 -9.4백만원이 함께 있음.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⑩ 9/30 퇴직 640,952,952원은 9월말 미지급(10월 지급 예정) → 9월말 '25 Drive 2 잔액 3,513,646,441원 중 자료로 설명되는 금액은 640,952,952원뿐이며 2,872,693,490원은 근거 없음(과다 계상 가능성). 11·12월 퇴직 예정 2건(Corporate Functions)은 금액 미기재 → '26 신규 959.5백만원의 근거 불충분. 시트 '회사자료 대사' 참조.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">회사 VRP 자료(4.06_VRP_2026 'Simulation') vs GL 대사</t>
+  </si>
+  <si>
+    <t xml:space="preserve">회사자료 원문(#, CC, BU, 퇴직일, VRP 추정액)을 그대로 옮기고 GL 사용(38160000 차변) 및 지급(62100747)과 비교. 금액 원 단위.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BU/Function</t>
+  </si>
+  <si>
+    <t xml:space="preserve">퇴직일</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VRP 추정액(회사)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">비고(회사)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GL 사용월</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GL 사용액</t>
+  </si>
+  <si>
+    <t xml:space="preserve">차이(회사-GL)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GL 지급액</t>
+  </si>
+  <si>
+    <t xml:space="preserve">검토 의견</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0000066792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">General Medicines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/31 퇴직 → 2월 급여대장(830000028) 지급. 차이 3.5백만원은 전직지원 1인분(3.5백만원) 포함으로 추정</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0000053716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">일치. 지급은 연금사업자 554.8백만원(차이 2.4백만원)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0000053799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6/30 퇴직 → 7월 급여대장(830000157) 지급, 일치</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9/30 퇴직, 9월말 미지급 → 10월 지급 여부 기간후 확인</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0000053698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corporate Functions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">planned</t>
+  </si>
+  <si>
+    <t xml:space="preserve">퇴직 예정(planned), 금액 미기재</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0000083311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9월말 잔액 대사 ('25 Drive 2 VRP, 38160000)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GL 9월말 '25 Drive 2 VRP 잔액</t>
+  </si>
+  <si>
+    <t xml:space="preserve">회사자료상 9월말 미지급 (#4, 9/30 퇴직)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">차이 (근거 없는 잔액)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">대상자·금액 근거 요청, 없으면 환입 검토</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GL 9월말 '26 신규 VRP 잔액 (Key market·Argos·Procurement·DD&amp;O)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">회사자료상 금액 (#5, #6 planned)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">금액 미기재 → 산정 근거 요청</t>
   </si>
   <si>
     <t xml:space="preserve">전표번호</t>
@@ -529,7 +635,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="19">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -582,11 +688,27 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="166" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -863,7 +985,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J53"/>
+  <dimension ref="A1:J54"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1847,8 +1969,22 @@
       <c r="I53" s="12"/>
       <c r="J53" s="12"/>
     </row>
+    <row r="54" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="B54" s="11"/>
+      <c r="C54" s="11"/>
+      <c r="D54" s="11"/>
+      <c r="E54" s="11"/>
+      <c r="F54" s="11"/>
+      <c r="G54" s="11"/>
+      <c r="H54" s="11"/>
+      <c r="I54" s="11"/>
+      <c r="J54" s="11"/>
+    </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="A45:J45"/>
     <mergeCell ref="A46:J46"/>
     <mergeCell ref="A47:J47"/>
@@ -1858,6 +1994,7 @@
     <mergeCell ref="A51:J51"/>
     <mergeCell ref="A52:J52"/>
     <mergeCell ref="A53:J53"/>
+    <mergeCell ref="A54:J54"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1870,6 +2007,414 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:K18"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="60"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="13" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="H4" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="I4" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="J4" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D5" s="17" t="n">
+        <v>46053</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>776740036</v>
+      </c>
+      <c r="F5" s="2"/>
+      <c r="G5" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="H5" s="7" t="n">
+        <f aca="false">SUMIFS(분개상세!$N$2:$N$101,분개상세!$I$2:$I$101,38160000,분개상세!$M$2:$M$101,"사용",분개상세!$B$2:$B$101,2,분개상세!$N$2:$N$101,"&gt;100000000")</f>
+        <v>773240036</v>
+      </c>
+      <c r="I5" s="7" t="n">
+        <f aca="false">E5-H5</f>
+        <v>3500000</v>
+      </c>
+      <c r="J5" s="7" t="n">
+        <f aca="false">SUMIFS('VRP 지급내역'!$H$2:$H$19,'VRP 지급내역'!$B$2:$B$19,2)</f>
+        <v>773240036</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D6" s="17" t="n">
+        <v>46142</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>552383939.0736</v>
+      </c>
+      <c r="F6" s="2"/>
+      <c r="G6" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="H6" s="7" t="n">
+        <f aca="false">SUMIFS(분개상세!$N$2:$N$101,분개상세!$I$2:$I$101,38160000,분개상세!$M$2:$M$101,"사용",분개상세!$B$2:$B$101,4,분개상세!$N$2:$N$101,"&gt;100000000")</f>
+        <v>552383939</v>
+      </c>
+      <c r="I6" s="7" t="n">
+        <f aca="false">E6-H6</f>
+        <v>0.0736000537872315</v>
+      </c>
+      <c r="J6" s="7" t="n">
+        <f aca="false">SUMIFS('VRP 지급내역'!$H$2:$H$19,'VRP 지급내역'!$B$2:$B$19,4)</f>
+        <v>554771272</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D7" s="17" t="n">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>742500000</v>
+      </c>
+      <c r="F7" s="2"/>
+      <c r="G7" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="H7" s="7" t="n">
+        <f aca="false">SUMIFS(분개상세!$N$2:$N$101,분개상세!$I$2:$I$101,38160000,분개상세!$M$2:$M$101,"사용",분개상세!$B$2:$B$101,7,분개상세!$N$2:$N$101,"&gt;100000000")</f>
+        <v>742500000</v>
+      </c>
+      <c r="I7" s="7" t="n">
+        <f aca="false">E7-H7</f>
+        <v>0</v>
+      </c>
+      <c r="J7" s="7" t="n">
+        <f aca="false">SUMIFS('VRP 지급내역'!$H$2:$H$19,'VRP 지급내역'!$B$2:$B$19,7)</f>
+        <v>742500000</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D8" s="17" t="n">
+        <v>46295</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>640952951.5</v>
+      </c>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D9" s="17" t="n">
+        <v>46356</v>
+      </c>
+      <c r="E9" s="7"/>
+      <c r="F9" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="G9" s="2"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D10" s="17" t="n">
+        <v>46387</v>
+      </c>
+      <c r="E10" s="7"/>
+      <c r="F10" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="G10" s="2"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="7" t="n">
+        <f aca="false">SUM(E5:E10)</f>
+        <v>2712576926.5736</v>
+      </c>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="7" t="n">
+        <f aca="false">SUM(H5:H10)</f>
+        <v>2068123975</v>
+      </c>
+      <c r="I11" s="7" t="n">
+        <f aca="false">SUM(I5:I10)</f>
+        <v>3500000.07360005</v>
+      </c>
+      <c r="J11" s="7" t="n">
+        <f aca="false">SUM(J5:J10)</f>
+        <v>2070511308</v>
+      </c>
+      <c r="K11" s="2"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="2"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="2"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="7" t="n">
+        <f aca="false">16873571611-SUMIFS(분개상세!$N$2:$N$101,분개상세!$I$2:$I$101,38160000,분개상세!$L$2:$L$101,"'25 Drive 2 (commercial)")</f>
+        <v>3513646441</v>
+      </c>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="2"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="7" t="n">
+        <f aca="false">E8</f>
+        <v>640952951.5</v>
+      </c>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="2"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="7" t="n">
+        <f aca="false">E14-E15</f>
+        <v>2872693489.5</v>
+      </c>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="7"/>
+      <c r="K16" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="7" t="n">
+        <f aca="false">-(SUMIFS(분개상세!$N$2:$N$101,분개상세!$I$2:$I$101,38160000,분개상세!$L$2:$L$101,"'26 Key market")+SUMIFS(분개상세!$N$2:$N$101,분개상세!$I$2:$I$101,38160000,분개상세!$L$2:$L$101,"'26 Argos")+SUMIFS(분개상세!$N$2:$N$101,분개상세!$I$2:$I$101,38160000,분개상세!$L$2:$L$101,"'26 Procurement transformation")+SUMIFS(분개상세!$N$2:$N$101,분개상세!$I$2:$I$101,38160000,분개상세!$L$2:$L$101,"'26 DD&amp;O Footprint"))</f>
+        <v>959537946</v>
+      </c>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="2"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -1893,47 +2438,47 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="B1" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="C1" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="D1" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="F1" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="G1" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="H1" s="13" t="s">
-        <v>68</v>
+      <c r="A1" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="E1" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="F1" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="G1" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="H1" s="18" t="s">
+        <v>103</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="J1" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="K1" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="L1" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="J1" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="K1" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="L1" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="M1" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="N1" s="13" t="s">
-        <v>73</v>
+      <c r="M1" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="N1" s="18" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1943,17 +2488,17 @@
       <c r="B2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="14" t="n">
+      <c r="C2" s="17" t="n">
         <v>46023</v>
       </c>
-      <c r="D2" s="14" t="n">
+      <c r="D2" s="17" t="n">
         <v>46022</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="n">
@@ -1963,14 +2508,14 @@
         <v>38160000</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="K2" s="2"/>
       <c r="L2" s="2" t="s">
         <v>30</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="N2" s="7" t="n">
         <v>1228771976</v>
@@ -1983,17 +2528,17 @@
       <c r="B3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="14" t="n">
+      <c r="C3" s="17" t="n">
         <v>46023</v>
       </c>
-      <c r="D3" s="14" t="n">
+      <c r="D3" s="17" t="n">
         <v>46022</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2" t="n">
@@ -2003,14 +2548,14 @@
         <v>38160000</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="K3" s="2"/>
       <c r="L3" s="2" t="s">
         <v>30</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="N3" s="7" t="n">
         <v>-14455123</v>
@@ -2023,17 +2568,17 @@
       <c r="B4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="14" t="n">
+      <c r="C4" s="17" t="n">
         <v>46023</v>
       </c>
-      <c r="D4" s="14" t="n">
+      <c r="D4" s="17" t="n">
         <v>46022</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2" t="n">
@@ -2043,14 +2588,14 @@
         <v>38160000</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="K4" s="2"/>
       <c r="L4" s="2" t="s">
         <v>30</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="N4" s="7" t="n">
         <v>-954316853</v>
@@ -2063,17 +2608,17 @@
       <c r="B5" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="14" t="n">
+      <c r="C5" s="17" t="n">
         <v>46023</v>
       </c>
-      <c r="D5" s="14" t="n">
+      <c r="D5" s="17" t="n">
         <v>46022</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2" t="n">
@@ -2083,14 +2628,14 @@
         <v>38160000</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
         <v>30</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="N5" s="7" t="n">
         <v>-260000000</v>
@@ -2103,30 +2648,30 @@
       <c r="B6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="14" t="n">
+      <c r="C6" s="17" t="n">
         <v>46053</v>
       </c>
-      <c r="D6" s="14" t="n">
+      <c r="D6" s="17" t="n">
         <v>46053</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2" t="n">
         <v>38160000</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="L6" s="6" t="s">
         <v>19</v>
@@ -2145,30 +2690,30 @@
       <c r="B7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="14" t="n">
+      <c r="C7" s="17" t="n">
         <v>46053</v>
       </c>
-      <c r="D7" s="14" t="n">
+      <c r="D7" s="17" t="n">
         <v>46053</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2" t="n">
         <v>38160000</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="L7" s="6" t="s">
         <v>19</v>
@@ -2187,30 +2732,30 @@
       <c r="B8" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="14" t="n">
+      <c r="C8" s="17" t="n">
         <v>46053</v>
       </c>
-      <c r="D8" s="14" t="n">
+      <c r="D8" s="17" t="n">
         <v>46053</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2" t="n">
         <v>38160000</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>19</v>
@@ -2229,30 +2774,30 @@
       <c r="B9" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C9" s="14" t="n">
+      <c r="C9" s="17" t="n">
         <v>46053</v>
       </c>
-      <c r="D9" s="14" t="n">
+      <c r="D9" s="17" t="n">
         <v>46053</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2" t="n">
         <v>38160000</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="L9" s="6" t="s">
         <v>19</v>
@@ -2271,30 +2816,30 @@
       <c r="B10" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C10" s="14" t="n">
+      <c r="C10" s="17" t="n">
         <v>46053</v>
       </c>
-      <c r="D10" s="14" t="n">
+      <c r="D10" s="17" t="n">
         <v>46053</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2" t="n">
         <v>38160000</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="L10" s="6" t="s">
         <v>19</v>
@@ -2313,30 +2858,30 @@
       <c r="B11" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="14" t="n">
+      <c r="C11" s="17" t="n">
         <v>46053</v>
       </c>
-      <c r="D11" s="14" t="n">
+      <c r="D11" s="17" t="n">
         <v>46053</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="H11" s="2"/>
       <c r="I11" s="2" t="n">
         <v>38160000</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="L11" s="6" t="s">
         <v>19</v>
@@ -2355,30 +2900,30 @@
       <c r="B12" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C12" s="14" t="n">
+      <c r="C12" s="17" t="n">
         <v>46053</v>
       </c>
-      <c r="D12" s="14" t="n">
+      <c r="D12" s="17" t="n">
         <v>46053</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="2" t="n">
         <v>38160000</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="L12" s="6" t="s">
         <v>19</v>
@@ -2397,30 +2942,30 @@
       <c r="B13" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C13" s="14" t="n">
+      <c r="C13" s="17" t="n">
         <v>46053</v>
       </c>
-      <c r="D13" s="14" t="n">
+      <c r="D13" s="17" t="n">
         <v>46053</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="H13" s="2"/>
       <c r="I13" s="2" t="n">
         <v>38160000</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="L13" s="6" t="s">
         <v>19</v>
@@ -2439,30 +2984,30 @@
       <c r="B14" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="14" t="n">
+      <c r="C14" s="17" t="n">
         <v>46053</v>
       </c>
-      <c r="D14" s="14" t="n">
+      <c r="D14" s="17" t="n">
         <v>46053</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="2" t="n">
         <v>38160000</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="L14" s="6" t="s">
         <v>19</v>
@@ -2481,30 +3026,30 @@
       <c r="B15" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C15" s="14" t="n">
+      <c r="C15" s="17" t="n">
         <v>46053</v>
       </c>
-      <c r="D15" s="14" t="n">
+      <c r="D15" s="17" t="n">
         <v>46053</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="H15" s="2"/>
       <c r="I15" s="2" t="n">
         <v>38160000</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="L15" s="6" t="s">
         <v>19</v>
@@ -2523,30 +3068,30 @@
       <c r="B16" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C16" s="14" t="n">
+      <c r="C16" s="17" t="n">
         <v>46053</v>
       </c>
-      <c r="D16" s="14" t="n">
+      <c r="D16" s="17" t="n">
         <v>46053</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="H16" s="2"/>
       <c r="I16" s="2" t="n">
         <v>38160000</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="L16" s="6" t="s">
         <v>19</v>
@@ -2565,30 +3110,30 @@
       <c r="B17" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C17" s="14" t="n">
+      <c r="C17" s="17" t="n">
         <v>46053</v>
       </c>
-      <c r="D17" s="14" t="n">
+      <c r="D17" s="17" t="n">
         <v>46053</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="H17" s="2"/>
       <c r="I17" s="2" t="n">
         <v>62100747</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="L17" s="6" t="s">
         <v>19</v>
@@ -2607,30 +3152,30 @@
       <c r="B18" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C18" s="14" t="n">
+      <c r="C18" s="17" t="n">
         <v>46053</v>
       </c>
-      <c r="D18" s="14" t="n">
+      <c r="D18" s="17" t="n">
         <v>46053</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="H18" s="2"/>
       <c r="I18" s="2" t="n">
         <v>62100747</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="L18" s="6" t="s">
         <v>19</v>
@@ -2649,30 +3194,30 @@
       <c r="B19" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C19" s="14" t="n">
+      <c r="C19" s="17" t="n">
         <v>46053</v>
       </c>
-      <c r="D19" s="14" t="n">
+      <c r="D19" s="17" t="n">
         <v>46053</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="H19" s="2"/>
       <c r="I19" s="2" t="n">
         <v>62100747</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="K19" s="6" t="s">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="L19" s="6" t="s">
         <v>19</v>
@@ -2691,30 +3236,30 @@
       <c r="B20" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C20" s="14" t="n">
+      <c r="C20" s="17" t="n">
         <v>46053</v>
       </c>
-      <c r="D20" s="14" t="n">
+      <c r="D20" s="17" t="n">
         <v>46053</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="H20" s="2"/>
       <c r="I20" s="2" t="n">
         <v>62100747</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="K20" s="6" t="s">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="L20" s="6" t="s">
         <v>19</v>
@@ -2733,30 +3278,30 @@
       <c r="B21" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C21" s="14" t="n">
+      <c r="C21" s="17" t="n">
         <v>46053</v>
       </c>
-      <c r="D21" s="14" t="n">
+      <c r="D21" s="17" t="n">
         <v>46053</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="H21" s="2"/>
       <c r="I21" s="2" t="n">
         <v>62100747</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="K21" s="6" t="s">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="L21" s="6" t="s">
         <v>19</v>
@@ -2775,30 +3320,30 @@
       <c r="B22" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C22" s="14" t="n">
+      <c r="C22" s="17" t="n">
         <v>46053</v>
       </c>
-      <c r="D22" s="14" t="n">
+      <c r="D22" s="17" t="n">
         <v>46053</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="H22" s="2"/>
       <c r="I22" s="2" t="n">
         <v>62100747</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="L22" s="6" t="s">
         <v>19</v>
@@ -2817,30 +3362,30 @@
       <c r="B23" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C23" s="14" t="n">
+      <c r="C23" s="17" t="n">
         <v>46053</v>
       </c>
-      <c r="D23" s="14" t="n">
+      <c r="D23" s="17" t="n">
         <v>46053</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="H23" s="2"/>
       <c r="I23" s="2" t="n">
         <v>62100747</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="K23" s="6" t="s">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="L23" s="6" t="s">
         <v>19</v>
@@ -2859,30 +3404,30 @@
       <c r="B24" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C24" s="14" t="n">
+      <c r="C24" s="17" t="n">
         <v>46053</v>
       </c>
-      <c r="D24" s="14" t="n">
+      <c r="D24" s="17" t="n">
         <v>46053</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="H24" s="2"/>
       <c r="I24" s="2" t="n">
         <v>62100747</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="K24" s="6" t="s">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="L24" s="6" t="s">
         <v>19</v>
@@ -2901,30 +3446,30 @@
       <c r="B25" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C25" s="14" t="n">
+      <c r="C25" s="17" t="n">
         <v>46053</v>
       </c>
-      <c r="D25" s="14" t="n">
+      <c r="D25" s="17" t="n">
         <v>46053</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="H25" s="2"/>
       <c r="I25" s="2" t="n">
         <v>62100747</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="K25" s="6" t="s">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="L25" s="6" t="s">
         <v>19</v>
@@ -2943,30 +3488,30 @@
       <c r="B26" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C26" s="14" t="n">
+      <c r="C26" s="17" t="n">
         <v>46053</v>
       </c>
-      <c r="D26" s="14" t="n">
+      <c r="D26" s="17" t="n">
         <v>46053</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="H26" s="2"/>
       <c r="I26" s="2" t="n">
         <v>62100747</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="K26" s="6" t="s">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="L26" s="6" t="s">
         <v>19</v>
@@ -2985,30 +3530,30 @@
       <c r="B27" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C27" s="14" t="n">
+      <c r="C27" s="17" t="n">
         <v>46053</v>
       </c>
-      <c r="D27" s="14" t="n">
+      <c r="D27" s="17" t="n">
         <v>46053</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="H27" s="2"/>
       <c r="I27" s="2" t="n">
         <v>62100747</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="K27" s="6" t="s">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="L27" s="6" t="s">
         <v>19</v>
@@ -3027,30 +3572,30 @@
       <c r="B28" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C28" s="14" t="n">
+      <c r="C28" s="17" t="n">
         <v>46081</v>
       </c>
-      <c r="D28" s="14" t="n">
+      <c r="D28" s="17" t="n">
         <v>46081</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="H28" s="2"/>
       <c r="I28" s="2" t="n">
         <v>38160000</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="K28" s="6" t="s">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="L28" s="6" t="s">
         <v>19</v>
@@ -3069,30 +3614,30 @@
       <c r="B29" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C29" s="14" t="n">
+      <c r="C29" s="17" t="n">
         <v>46081</v>
       </c>
-      <c r="D29" s="14" t="n">
+      <c r="D29" s="17" t="n">
         <v>46081</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="H29" s="2"/>
       <c r="I29" s="2" t="n">
         <v>38160000</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="K29" s="6" t="s">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="L29" s="6" t="s">
         <v>19</v>
@@ -3111,30 +3656,30 @@
       <c r="B30" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C30" s="14" t="n">
+      <c r="C30" s="17" t="n">
         <v>46081</v>
       </c>
-      <c r="D30" s="14" t="n">
+      <c r="D30" s="17" t="n">
         <v>46081</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="H30" s="2"/>
       <c r="I30" s="2" t="n">
         <v>38160000</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="K30" s="6" t="s">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="L30" s="6" t="s">
         <v>19</v>
@@ -3153,30 +3698,30 @@
       <c r="B31" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C31" s="14" t="n">
+      <c r="C31" s="17" t="n">
         <v>46081</v>
       </c>
-      <c r="D31" s="14" t="n">
+      <c r="D31" s="17" t="n">
         <v>46081</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="H31" s="2"/>
       <c r="I31" s="2" t="n">
         <v>38160000</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="K31" s="6" t="s">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="L31" s="6" t="s">
         <v>19</v>
@@ -3195,30 +3740,30 @@
       <c r="B32" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C32" s="14" t="n">
+      <c r="C32" s="17" t="n">
         <v>46081</v>
       </c>
-      <c r="D32" s="14" t="n">
+      <c r="D32" s="17" t="n">
         <v>46081</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="H32" s="2"/>
       <c r="I32" s="2" t="n">
         <v>38160000</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="K32" s="6" t="s">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="L32" s="6" t="s">
         <v>19</v>
@@ -3237,30 +3782,30 @@
       <c r="B33" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C33" s="14" t="n">
+      <c r="C33" s="17" t="n">
         <v>46081</v>
       </c>
-      <c r="D33" s="14" t="n">
+      <c r="D33" s="17" t="n">
         <v>46081</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="H33" s="2"/>
       <c r="I33" s="2" t="n">
         <v>38160000</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="K33" s="6" t="s">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="L33" s="6" t="s">
         <v>19</v>
@@ -3279,30 +3824,30 @@
       <c r="B34" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C34" s="14" t="n">
+      <c r="C34" s="17" t="n">
         <v>46081</v>
       </c>
-      <c r="D34" s="14" t="n">
+      <c r="D34" s="17" t="n">
         <v>46081</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="H34" s="2"/>
       <c r="I34" s="2" t="n">
         <v>38160000</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="K34" s="6" t="s">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="L34" s="6" t="s">
         <v>19</v>
@@ -3321,30 +3866,30 @@
       <c r="B35" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C35" s="14" t="n">
+      <c r="C35" s="17" t="n">
         <v>46081</v>
       </c>
-      <c r="D35" s="14" t="n">
+      <c r="D35" s="17" t="n">
         <v>46081</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="H35" s="2"/>
       <c r="I35" s="2" t="n">
         <v>38160000</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="K35" s="6" t="s">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="L35" s="6" t="s">
         <v>19</v>
@@ -3363,30 +3908,30 @@
       <c r="B36" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C36" s="14" t="n">
+      <c r="C36" s="17" t="n">
         <v>46081</v>
       </c>
-      <c r="D36" s="14" t="n">
+      <c r="D36" s="17" t="n">
         <v>46081</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="H36" s="2"/>
       <c r="I36" s="2" t="n">
         <v>38160000</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="K36" s="6" t="s">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="L36" s="6" t="s">
         <v>19</v>
@@ -3405,30 +3950,30 @@
       <c r="B37" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C37" s="14" t="n">
+      <c r="C37" s="17" t="n">
         <v>46081</v>
       </c>
-      <c r="D37" s="14" t="n">
+      <c r="D37" s="17" t="n">
         <v>46081</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="H37" s="2"/>
       <c r="I37" s="2" t="n">
         <v>38160000</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="K37" s="6" t="s">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="L37" s="6" t="s">
         <v>19</v>
@@ -3447,30 +3992,30 @@
       <c r="B38" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C38" s="14" t="n">
+      <c r="C38" s="17" t="n">
         <v>46081</v>
       </c>
-      <c r="D38" s="14" t="n">
+      <c r="D38" s="17" t="n">
         <v>46081</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="H38" s="2"/>
       <c r="I38" s="2" t="n">
         <v>38160000</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="K38" s="6" t="s">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="L38" s="6" t="s">
         <v>19</v>
@@ -3489,30 +4034,30 @@
       <c r="B39" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C39" s="14" t="n">
+      <c r="C39" s="17" t="n">
         <v>46081</v>
       </c>
-      <c r="D39" s="14" t="n">
+      <c r="D39" s="17" t="n">
         <v>46081</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="H39" s="2"/>
       <c r="I39" s="2" t="n">
         <v>62100747</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="K39" s="6" t="s">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="L39" s="6" t="s">
         <v>19</v>
@@ -3531,30 +4076,30 @@
       <c r="B40" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C40" s="14" t="n">
+      <c r="C40" s="17" t="n">
         <v>46081</v>
       </c>
-      <c r="D40" s="14" t="n">
+      <c r="D40" s="17" t="n">
         <v>46081</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="H40" s="2"/>
       <c r="I40" s="2" t="n">
         <v>62100747</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="K40" s="6" t="s">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="L40" s="6" t="s">
         <v>19</v>
@@ -3573,30 +4118,30 @@
       <c r="B41" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C41" s="14" t="n">
+      <c r="C41" s="17" t="n">
         <v>46081</v>
       </c>
-      <c r="D41" s="14" t="n">
+      <c r="D41" s="17" t="n">
         <v>46081</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="H41" s="2"/>
       <c r="I41" s="2" t="n">
         <v>62100747</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="K41" s="6" t="s">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="L41" s="6" t="s">
         <v>19</v>
@@ -3615,30 +4160,30 @@
       <c r="B42" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C42" s="14" t="n">
+      <c r="C42" s="17" t="n">
         <v>46081</v>
       </c>
-      <c r="D42" s="14" t="n">
+      <c r="D42" s="17" t="n">
         <v>46081</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="H42" s="2"/>
       <c r="I42" s="2" t="n">
         <v>62100747</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="K42" s="6" t="s">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="L42" s="6" t="s">
         <v>19</v>
@@ -3657,30 +4202,30 @@
       <c r="B43" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C43" s="14" t="n">
+      <c r="C43" s="17" t="n">
         <v>46081</v>
       </c>
-      <c r="D43" s="14" t="n">
+      <c r="D43" s="17" t="n">
         <v>46081</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="H43" s="2"/>
       <c r="I43" s="2" t="n">
         <v>62100747</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="K43" s="6" t="s">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="L43" s="6" t="s">
         <v>19</v>
@@ -3699,30 +4244,30 @@
       <c r="B44" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C44" s="14" t="n">
+      <c r="C44" s="17" t="n">
         <v>46081</v>
       </c>
-      <c r="D44" s="14" t="n">
+      <c r="D44" s="17" t="n">
         <v>46081</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="H44" s="2"/>
       <c r="I44" s="2" t="n">
         <v>62100747</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="K44" s="6" t="s">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="L44" s="6" t="s">
         <v>19</v>
@@ -3741,30 +4286,30 @@
       <c r="B45" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C45" s="14" t="n">
+      <c r="C45" s="17" t="n">
         <v>46081</v>
       </c>
-      <c r="D45" s="14" t="n">
+      <c r="D45" s="17" t="n">
         <v>46081</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="H45" s="2"/>
       <c r="I45" s="2" t="n">
         <v>62100747</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="K45" s="6" t="s">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="L45" s="6" t="s">
         <v>19</v>
@@ -3783,30 +4328,30 @@
       <c r="B46" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C46" s="14" t="n">
+      <c r="C46" s="17" t="n">
         <v>46081</v>
       </c>
-      <c r="D46" s="14" t="n">
+      <c r="D46" s="17" t="n">
         <v>46081</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="H46" s="2"/>
       <c r="I46" s="2" t="n">
         <v>62100747</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="K46" s="6" t="s">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="L46" s="6" t="s">
         <v>19</v>
@@ -3825,30 +4370,30 @@
       <c r="B47" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C47" s="14" t="n">
+      <c r="C47" s="17" t="n">
         <v>46081</v>
       </c>
-      <c r="D47" s="14" t="n">
+      <c r="D47" s="17" t="n">
         <v>46081</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="H47" s="2"/>
       <c r="I47" s="2" t="n">
         <v>62100747</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="K47" s="6" t="s">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="L47" s="6" t="s">
         <v>19</v>
@@ -3867,30 +4412,30 @@
       <c r="B48" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C48" s="14" t="n">
+      <c r="C48" s="17" t="n">
         <v>46081</v>
       </c>
-      <c r="D48" s="14" t="n">
+      <c r="D48" s="17" t="n">
         <v>46081</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="H48" s="2"/>
       <c r="I48" s="2" t="n">
         <v>62100747</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="K48" s="6" t="s">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="L48" s="6" t="s">
         <v>19</v>
@@ -3909,30 +4454,30 @@
       <c r="B49" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C49" s="14" t="n">
+      <c r="C49" s="17" t="n">
         <v>46081</v>
       </c>
-      <c r="D49" s="14" t="n">
+      <c r="D49" s="17" t="n">
         <v>46081</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="H49" s="2"/>
       <c r="I49" s="2" t="n">
         <v>62100747</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="K49" s="6" t="s">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="L49" s="6" t="s">
         <v>19</v>
@@ -3951,20 +4496,20 @@
       <c r="B50" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C50" s="14" t="n">
+      <c r="C50" s="17" t="n">
         <v>46112</v>
       </c>
-      <c r="D50" s="14" t="n">
+      <c r="D50" s="17" t="n">
         <v>46112</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="H50" s="2" t="n">
         <v>120000071</v>
@@ -3973,16 +4518,16 @@
         <v>38160000</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="K50" s="6" t="s">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="L50" s="6" t="s">
         <v>19</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="N50" s="7" t="n">
         <v>2271351872</v>
@@ -3995,20 +4540,20 @@
       <c r="B51" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C51" s="14" t="n">
+      <c r="C51" s="17" t="n">
         <v>46112</v>
       </c>
-      <c r="D51" s="14" t="n">
+      <c r="D51" s="17" t="n">
         <v>46112</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="H51" s="2" t="n">
         <v>120000071</v>
@@ -4017,16 +4562,16 @@
         <v>42910311</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="K51" s="6" t="s">
-        <v>86</v>
+        <v>121</v>
       </c>
       <c r="L51" s="6" t="s">
         <v>19</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="N51" s="7" t="n">
         <v>80500000</v>
@@ -4039,20 +4584,20 @@
       <c r="B52" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C52" s="14" t="n">
+      <c r="C52" s="17" t="n">
         <v>46112</v>
       </c>
-      <c r="D52" s="14" t="n">
+      <c r="D52" s="17" t="n">
         <v>46112</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="H52" s="2" t="n">
         <v>120000071</v>
@@ -4061,16 +4606,16 @@
         <v>70051000</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>87</v>
+        <v>122</v>
       </c>
       <c r="K52" s="6" t="s">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="L52" s="6" t="s">
         <v>19</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="N52" s="7" t="n">
         <v>-2271351872</v>
@@ -4083,20 +4628,20 @@
       <c r="B53" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C53" s="14" t="n">
+      <c r="C53" s="17" t="n">
         <v>46112</v>
       </c>
-      <c r="D53" s="14" t="n">
+      <c r="D53" s="17" t="n">
         <v>46112</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G53" s="6" t="s">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="H53" s="2" t="n">
         <v>120000071</v>
@@ -4105,16 +4650,16 @@
         <v>70051000</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>87</v>
+        <v>122</v>
       </c>
       <c r="K53" s="6" t="s">
-        <v>86</v>
+        <v>121</v>
       </c>
       <c r="L53" s="6" t="s">
         <v>19</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="N53" s="7" t="n">
         <v>-80500000</v>
@@ -4127,20 +4672,20 @@
       <c r="B54" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C54" s="14" t="n">
+      <c r="C54" s="17" t="n">
         <v>46112</v>
       </c>
-      <c r="D54" s="14" t="n">
+      <c r="D54" s="17" t="n">
         <v>46112</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F54" s="6" t="s">
-        <v>88</v>
+        <v>123</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="H54" s="2" t="n">
         <v>120000070</v>
@@ -4149,16 +4694,16 @@
         <v>38160000</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="K54" s="6" t="s">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="L54" s="6" t="s">
         <v>19</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="N54" s="7" t="n">
         <v>-2271351872</v>
@@ -4171,20 +4716,20 @@
       <c r="B55" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C55" s="14" t="n">
+      <c r="C55" s="17" t="n">
         <v>46112</v>
       </c>
-      <c r="D55" s="14" t="n">
+      <c r="D55" s="17" t="n">
         <v>46112</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F55" s="6" t="s">
-        <v>88</v>
+        <v>123</v>
       </c>
       <c r="G55" s="6" t="s">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="H55" s="2" t="n">
         <v>120000070</v>
@@ -4193,16 +4738,16 @@
         <v>42910311</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="K55" s="6" t="s">
-        <v>86</v>
+        <v>121</v>
       </c>
       <c r="L55" s="6" t="s">
         <v>19</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="N55" s="7" t="n">
         <v>-80500000</v>
@@ -4215,20 +4760,20 @@
       <c r="B56" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C56" s="14" t="n">
+      <c r="C56" s="17" t="n">
         <v>46112</v>
       </c>
-      <c r="D56" s="14" t="n">
+      <c r="D56" s="17" t="n">
         <v>46112</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F56" s="6" t="s">
-        <v>88</v>
+        <v>123</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="H56" s="2" t="n">
         <v>120000070</v>
@@ -4237,16 +4782,16 @@
         <v>70051000</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>87</v>
+        <v>122</v>
       </c>
       <c r="K56" s="6" t="s">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="L56" s="6" t="s">
         <v>19</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="N56" s="7" t="n">
         <v>2271351872</v>
@@ -4259,20 +4804,20 @@
       <c r="B57" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C57" s="14" t="n">
+      <c r="C57" s="17" t="n">
         <v>46112</v>
       </c>
-      <c r="D57" s="14" t="n">
+      <c r="D57" s="17" t="n">
         <v>46112</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F57" s="6" t="s">
-        <v>88</v>
+        <v>123</v>
       </c>
       <c r="G57" s="6" t="s">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="H57" s="2" t="n">
         <v>120000070</v>
@@ -4281,16 +4826,16 @@
         <v>70051000</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>87</v>
+        <v>122</v>
       </c>
       <c r="K57" s="6" t="s">
-        <v>86</v>
+        <v>121</v>
       </c>
       <c r="L57" s="6" t="s">
         <v>19</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="N57" s="7" t="n">
         <v>80500000</v>
@@ -4303,30 +4848,30 @@
       <c r="B58" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C58" s="14" t="n">
+      <c r="C58" s="17" t="n">
         <v>46112</v>
       </c>
-      <c r="D58" s="14" t="n">
+      <c r="D58" s="17" t="n">
         <v>46112</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F58" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="H58" s="2"/>
       <c r="I58" s="2" t="n">
         <v>38160000</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="K58" s="6" t="s">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="L58" s="6" t="s">
         <v>19</v>
@@ -4345,30 +4890,30 @@
       <c r="B59" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C59" s="14" t="n">
+      <c r="C59" s="17" t="n">
         <v>46112</v>
       </c>
-      <c r="D59" s="14" t="n">
+      <c r="D59" s="17" t="n">
         <v>46112</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F59" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G59" s="6" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="H59" s="2"/>
       <c r="I59" s="2" t="n">
         <v>42910311</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="K59" s="6" t="s">
-        <v>86</v>
+        <v>121</v>
       </c>
       <c r="L59" s="6" t="s">
         <v>19</v>
@@ -4387,30 +4932,30 @@
       <c r="B60" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C60" s="14" t="n">
+      <c r="C60" s="17" t="n">
         <v>46112</v>
       </c>
-      <c r="D60" s="14" t="n">
+      <c r="D60" s="17" t="n">
         <v>46112</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F60" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="H60" s="2"/>
       <c r="I60" s="2" t="n">
         <v>42910311</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="K60" s="6" t="s">
-        <v>89</v>
+        <v>124</v>
       </c>
       <c r="L60" s="6" t="s">
         <v>21</v>
@@ -4429,30 +4974,30 @@
       <c r="B61" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C61" s="14" t="n">
+      <c r="C61" s="17" t="n">
         <v>46112</v>
       </c>
-      <c r="D61" s="14" t="n">
+      <c r="D61" s="17" t="n">
         <v>46112</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F61" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G61" s="6" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="H61" s="2"/>
       <c r="I61" s="2" t="n">
         <v>68063200</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>90</v>
+        <v>125</v>
       </c>
       <c r="K61" s="6" t="s">
-        <v>89</v>
+        <v>124</v>
       </c>
       <c r="L61" s="6" t="s">
         <v>21</v>
@@ -4471,30 +5016,30 @@
       <c r="B62" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C62" s="14" t="n">
+      <c r="C62" s="17" t="n">
         <v>46112</v>
       </c>
-      <c r="D62" s="14" t="n">
+      <c r="D62" s="17" t="n">
         <v>46112</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F62" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="H62" s="2"/>
       <c r="I62" s="2" t="n">
         <v>70051000</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>87</v>
+        <v>122</v>
       </c>
       <c r="K62" s="6" t="s">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="L62" s="6" t="s">
         <v>19</v>
@@ -4513,30 +5058,30 @@
       <c r="B63" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C63" s="14" t="n">
+      <c r="C63" s="17" t="n">
         <v>46112</v>
       </c>
-      <c r="D63" s="14" t="n">
+      <c r="D63" s="17" t="n">
         <v>46112</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F63" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G63" s="6" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="H63" s="2"/>
       <c r="I63" s="2" t="n">
         <v>70051000</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>87</v>
+        <v>122</v>
       </c>
       <c r="K63" s="6" t="s">
-        <v>86</v>
+        <v>121</v>
       </c>
       <c r="L63" s="6" t="s">
         <v>19</v>
@@ -4555,30 +5100,30 @@
       <c r="B64" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C64" s="14" t="n">
+      <c r="C64" s="17" t="n">
         <v>46142</v>
       </c>
-      <c r="D64" s="14" t="n">
+      <c r="D64" s="17" t="n">
         <v>46142</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F64" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>91</v>
+        <v>126</v>
       </c>
       <c r="H64" s="2"/>
       <c r="I64" s="2" t="n">
         <v>38160000</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="K64" s="6" t="s">
-        <v>92</v>
+        <v>127</v>
       </c>
       <c r="L64" s="6" t="s">
         <v>23</v>
@@ -4597,30 +5142,30 @@
       <c r="B65" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C65" s="14" t="n">
+      <c r="C65" s="17" t="n">
         <v>46142</v>
       </c>
-      <c r="D65" s="14" t="n">
+      <c r="D65" s="17" t="n">
         <v>46142</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F65" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G65" s="6" t="s">
-        <v>91</v>
+        <v>126</v>
       </c>
       <c r="H65" s="2"/>
       <c r="I65" s="2" t="n">
         <v>38160000</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="K65" s="6" t="s">
-        <v>93</v>
+        <v>128</v>
       </c>
       <c r="L65" s="6" t="s">
         <v>25</v>
@@ -4639,30 +5184,30 @@
       <c r="B66" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C66" s="14" t="n">
+      <c r="C66" s="17" t="n">
         <v>46142</v>
       </c>
-      <c r="D66" s="14" t="n">
+      <c r="D66" s="17" t="n">
         <v>46142</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F66" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>91</v>
+        <v>126</v>
       </c>
       <c r="H66" s="2"/>
       <c r="I66" s="2" t="n">
         <v>38160000</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="K66" s="6" t="s">
-        <v>94</v>
+        <v>129</v>
       </c>
       <c r="L66" s="6" t="s">
         <v>26</v>
@@ -4681,30 +5226,30 @@
       <c r="B67" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C67" s="14" t="n">
+      <c r="C67" s="17" t="n">
         <v>46142</v>
       </c>
-      <c r="D67" s="14" t="n">
+      <c r="D67" s="17" t="n">
         <v>46142</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F67" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G67" s="6" t="s">
-        <v>91</v>
+        <v>126</v>
       </c>
       <c r="H67" s="2"/>
       <c r="I67" s="2" t="n">
         <v>42910311</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="K67" s="6" t="s">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="L67" s="6" t="s">
         <v>23</v>
@@ -4723,30 +5268,30 @@
       <c r="B68" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C68" s="14" t="n">
+      <c r="C68" s="17" t="n">
         <v>46142</v>
       </c>
-      <c r="D68" s="14" t="n">
+      <c r="D68" s="17" t="n">
         <v>46142</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F68" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>91</v>
+        <v>126</v>
       </c>
       <c r="H68" s="2"/>
       <c r="I68" s="2" t="n">
         <v>42910311</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="K68" s="6" t="s">
-        <v>96</v>
+        <v>131</v>
       </c>
       <c r="L68" s="6" t="s">
         <v>25</v>
@@ -4765,30 +5310,30 @@
       <c r="B69" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C69" s="14" t="n">
+      <c r="C69" s="17" t="n">
         <v>46142</v>
       </c>
-      <c r="D69" s="14" t="n">
+      <c r="D69" s="17" t="n">
         <v>46142</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F69" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G69" s="6" t="s">
-        <v>91</v>
+        <v>126</v>
       </c>
       <c r="H69" s="2"/>
       <c r="I69" s="2" t="n">
         <v>42910311</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="K69" s="6" t="s">
-        <v>97</v>
+        <v>132</v>
       </c>
       <c r="L69" s="6" t="s">
         <v>26</v>
@@ -4807,30 +5352,30 @@
       <c r="B70" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C70" s="14" t="n">
+      <c r="C70" s="17" t="n">
         <v>46142</v>
       </c>
-      <c r="D70" s="14" t="n">
+      <c r="D70" s="17" t="n">
         <v>46142</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F70" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>91</v>
+        <v>126</v>
       </c>
       <c r="H70" s="2"/>
       <c r="I70" s="2" t="n">
         <v>70051000</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>87</v>
+        <v>122</v>
       </c>
       <c r="K70" s="6" t="s">
-        <v>92</v>
+        <v>127</v>
       </c>
       <c r="L70" s="6" t="s">
         <v>23</v>
@@ -4849,30 +5394,30 @@
       <c r="B71" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C71" s="14" t="n">
+      <c r="C71" s="17" t="n">
         <v>46142</v>
       </c>
-      <c r="D71" s="14" t="n">
+      <c r="D71" s="17" t="n">
         <v>46142</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F71" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G71" s="6" t="s">
-        <v>91</v>
+        <v>126</v>
       </c>
       <c r="H71" s="2"/>
       <c r="I71" s="2" t="n">
         <v>70051000</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>87</v>
+        <v>122</v>
       </c>
       <c r="K71" s="6" t="s">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="L71" s="6" t="s">
         <v>23</v>
@@ -4891,30 +5436,30 @@
       <c r="B72" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C72" s="14" t="n">
+      <c r="C72" s="17" t="n">
         <v>46142</v>
       </c>
-      <c r="D72" s="14" t="n">
+      <c r="D72" s="17" t="n">
         <v>46142</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F72" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>91</v>
+        <v>126</v>
       </c>
       <c r="H72" s="2"/>
       <c r="I72" s="2" t="n">
         <v>70051000</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>87</v>
+        <v>122</v>
       </c>
       <c r="K72" s="6" t="s">
-        <v>93</v>
+        <v>128</v>
       </c>
       <c r="L72" s="6" t="s">
         <v>25</v>
@@ -4933,30 +5478,30 @@
       <c r="B73" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C73" s="14" t="n">
+      <c r="C73" s="17" t="n">
         <v>46142</v>
       </c>
-      <c r="D73" s="14" t="n">
+      <c r="D73" s="17" t="n">
         <v>46142</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F73" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G73" s="6" t="s">
-        <v>91</v>
+        <v>126</v>
       </c>
       <c r="H73" s="2"/>
       <c r="I73" s="2" t="n">
         <v>70051000</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>87</v>
+        <v>122</v>
       </c>
       <c r="K73" s="6" t="s">
-        <v>96</v>
+        <v>131</v>
       </c>
       <c r="L73" s="6" t="s">
         <v>25</v>
@@ -4975,30 +5520,30 @@
       <c r="B74" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C74" s="14" t="n">
+      <c r="C74" s="17" t="n">
         <v>46142</v>
       </c>
-      <c r="D74" s="14" t="n">
+      <c r="D74" s="17" t="n">
         <v>46142</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F74" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>91</v>
+        <v>126</v>
       </c>
       <c r="H74" s="2"/>
       <c r="I74" s="2" t="n">
         <v>70051000</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>87</v>
+        <v>122</v>
       </c>
       <c r="K74" s="6" t="s">
-        <v>94</v>
+        <v>129</v>
       </c>
       <c r="L74" s="6" t="s">
         <v>26</v>
@@ -5017,30 +5562,30 @@
       <c r="B75" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C75" s="14" t="n">
+      <c r="C75" s="17" t="n">
         <v>46142</v>
       </c>
-      <c r="D75" s="14" t="n">
+      <c r="D75" s="17" t="n">
         <v>46142</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F75" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G75" s="6" t="s">
-        <v>91</v>
+        <v>126</v>
       </c>
       <c r="H75" s="2"/>
       <c r="I75" s="2" t="n">
         <v>70051000</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>87</v>
+        <v>122</v>
       </c>
       <c r="K75" s="6" t="s">
-        <v>97</v>
+        <v>132</v>
       </c>
       <c r="L75" s="6" t="s">
         <v>26</v>
@@ -5059,30 +5604,30 @@
       <c r="B76" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C76" s="14" t="n">
+      <c r="C76" s="17" t="n">
         <v>46142</v>
       </c>
-      <c r="D76" s="14" t="n">
+      <c r="D76" s="17" t="n">
         <v>46142</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F76" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>98</v>
+        <v>133</v>
       </c>
       <c r="H76" s="2"/>
       <c r="I76" s="2" t="n">
         <v>38160000</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="K76" s="6" t="s">
-        <v>99</v>
+        <v>134</v>
       </c>
       <c r="L76" s="6" t="s">
         <v>19</v>
@@ -5101,30 +5646,30 @@
       <c r="B77" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C77" s="14" t="n">
+      <c r="C77" s="17" t="n">
         <v>46142</v>
       </c>
-      <c r="D77" s="14" t="n">
+      <c r="D77" s="17" t="n">
         <v>46142</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F77" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G77" s="6" t="s">
-        <v>98</v>
+        <v>133</v>
       </c>
       <c r="H77" s="2"/>
       <c r="I77" s="2" t="n">
         <v>42910311</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="K77" s="6" t="s">
-        <v>100</v>
+        <v>135</v>
       </c>
       <c r="L77" s="6" t="s">
         <v>19</v>
@@ -5143,30 +5688,30 @@
       <c r="B78" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C78" s="14" t="n">
+      <c r="C78" s="17" t="n">
         <v>46142</v>
       </c>
-      <c r="D78" s="14" t="n">
+      <c r="D78" s="17" t="n">
         <v>46142</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F78" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>98</v>
+        <v>133</v>
       </c>
       <c r="H78" s="2"/>
       <c r="I78" s="2" t="n">
         <v>62100747</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="K78" s="6" t="s">
-        <v>99</v>
+        <v>134</v>
       </c>
       <c r="L78" s="6" t="s">
         <v>19</v>
@@ -5185,30 +5730,30 @@
       <c r="B79" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C79" s="14" t="n">
+      <c r="C79" s="17" t="n">
         <v>46142</v>
       </c>
-      <c r="D79" s="14" t="n">
+      <c r="D79" s="17" t="n">
         <v>46142</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F79" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G79" s="6" t="s">
-        <v>98</v>
+        <v>133</v>
       </c>
       <c r="H79" s="2"/>
       <c r="I79" s="2" t="n">
         <v>68063200</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>90</v>
+        <v>125</v>
       </c>
       <c r="K79" s="6" t="s">
-        <v>100</v>
+        <v>135</v>
       </c>
       <c r="L79" s="6" t="s">
         <v>19</v>
@@ -5227,30 +5772,30 @@
       <c r="B80" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C80" s="14" t="n">
+      <c r="C80" s="17" t="n">
         <v>46142</v>
       </c>
-      <c r="D80" s="14" t="n">
+      <c r="D80" s="17" t="n">
         <v>46142</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F80" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>98</v>
+        <v>133</v>
       </c>
       <c r="H80" s="2"/>
       <c r="I80" s="2" t="n">
         <v>68063200</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>90</v>
+        <v>125</v>
       </c>
       <c r="K80" s="6" t="s">
-        <v>100</v>
+        <v>135</v>
       </c>
       <c r="L80" s="6" t="s">
         <v>19</v>
@@ -5269,30 +5814,30 @@
       <c r="B81" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C81" s="14" t="n">
+      <c r="C81" s="17" t="n">
         <v>46142</v>
       </c>
-      <c r="D81" s="14" t="n">
+      <c r="D81" s="17" t="n">
         <v>46142</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F81" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G81" s="6" t="s">
-        <v>98</v>
+        <v>133</v>
       </c>
       <c r="H81" s="2"/>
       <c r="I81" s="2" t="n">
         <v>68063200</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>90</v>
+        <v>125</v>
       </c>
       <c r="K81" s="6" t="s">
-        <v>100</v>
+        <v>135</v>
       </c>
       <c r="L81" s="6" t="s">
         <v>19</v>
@@ -5311,30 +5856,30 @@
       <c r="B82" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C82" s="14" t="n">
+      <c r="C82" s="17" t="n">
         <v>46173</v>
       </c>
-      <c r="D82" s="14" t="n">
+      <c r="D82" s="17" t="n">
         <v>46173</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F82" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>91</v>
+        <v>126</v>
       </c>
       <c r="H82" s="2"/>
       <c r="I82" s="2" t="n">
         <v>38160000</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="K82" s="6" t="s">
-        <v>101</v>
+        <v>136</v>
       </c>
       <c r="L82" s="6" t="s">
         <v>28</v>
@@ -5353,30 +5898,30 @@
       <c r="B83" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C83" s="14" t="n">
+      <c r="C83" s="17" t="n">
         <v>46173</v>
       </c>
-      <c r="D83" s="14" t="n">
+      <c r="D83" s="17" t="n">
         <v>46173</v>
       </c>
       <c r="E83" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F83" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G83" s="6" t="s">
-        <v>91</v>
+        <v>126</v>
       </c>
       <c r="H83" s="2"/>
       <c r="I83" s="2" t="n">
         <v>38160000</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="K83" s="6" t="s">
-        <v>102</v>
+        <v>137</v>
       </c>
       <c r="L83" s="6" t="s">
         <v>29</v>
@@ -5395,30 +5940,30 @@
       <c r="B84" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C84" s="14" t="n">
+      <c r="C84" s="17" t="n">
         <v>46173</v>
       </c>
-      <c r="D84" s="14" t="n">
+      <c r="D84" s="17" t="n">
         <v>46173</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F84" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>91</v>
+        <v>126</v>
       </c>
       <c r="H84" s="2"/>
       <c r="I84" s="2" t="n">
         <v>42910311</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="K84" s="6" t="s">
-        <v>103</v>
+        <v>138</v>
       </c>
       <c r="L84" s="6" t="s">
         <v>28</v>
@@ -5437,30 +5982,30 @@
       <c r="B85" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C85" s="14" t="n">
+      <c r="C85" s="17" t="n">
         <v>46173</v>
       </c>
-      <c r="D85" s="14" t="n">
+      <c r="D85" s="17" t="n">
         <v>46173</v>
       </c>
       <c r="E85" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F85" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G85" s="6" t="s">
-        <v>91</v>
+        <v>126</v>
       </c>
       <c r="H85" s="2"/>
       <c r="I85" s="2" t="n">
         <v>42910311</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="K85" s="6" t="s">
-        <v>104</v>
+        <v>139</v>
       </c>
       <c r="L85" s="6" t="s">
         <v>29</v>
@@ -5479,30 +6024,30 @@
       <c r="B86" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C86" s="14" t="n">
+      <c r="C86" s="17" t="n">
         <v>46173</v>
       </c>
-      <c r="D86" s="14" t="n">
+      <c r="D86" s="17" t="n">
         <v>46173</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F86" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>91</v>
+        <v>126</v>
       </c>
       <c r="H86" s="2"/>
       <c r="I86" s="2" t="n">
         <v>70051000</v>
       </c>
       <c r="J86" s="2" t="s">
-        <v>87</v>
+        <v>122</v>
       </c>
       <c r="K86" s="6" t="s">
-        <v>101</v>
+        <v>136</v>
       </c>
       <c r="L86" s="6" t="s">
         <v>28</v>
@@ -5521,30 +6066,30 @@
       <c r="B87" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C87" s="14" t="n">
+      <c r="C87" s="17" t="n">
         <v>46173</v>
       </c>
-      <c r="D87" s="14" t="n">
+      <c r="D87" s="17" t="n">
         <v>46173</v>
       </c>
       <c r="E87" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F87" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G87" s="6" t="s">
-        <v>91</v>
+        <v>126</v>
       </c>
       <c r="H87" s="2"/>
       <c r="I87" s="2" t="n">
         <v>70051000</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>87</v>
+        <v>122</v>
       </c>
       <c r="K87" s="6" t="s">
-        <v>103</v>
+        <v>138</v>
       </c>
       <c r="L87" s="6" t="s">
         <v>28</v>
@@ -5563,30 +6108,30 @@
       <c r="B88" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C88" s="14" t="n">
+      <c r="C88" s="17" t="n">
         <v>46173</v>
       </c>
-      <c r="D88" s="14" t="n">
+      <c r="D88" s="17" t="n">
         <v>46173</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F88" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>91</v>
+        <v>126</v>
       </c>
       <c r="H88" s="2"/>
       <c r="I88" s="2" t="n">
         <v>70051000</v>
       </c>
       <c r="J88" s="2" t="s">
-        <v>87</v>
+        <v>122</v>
       </c>
       <c r="K88" s="6" t="s">
-        <v>102</v>
+        <v>137</v>
       </c>
       <c r="L88" s="6" t="s">
         <v>29</v>
@@ -5605,30 +6150,30 @@
       <c r="B89" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C89" s="14" t="n">
+      <c r="C89" s="17" t="n">
         <v>46173</v>
       </c>
-      <c r="D89" s="14" t="n">
+      <c r="D89" s="17" t="n">
         <v>46173</v>
       </c>
       <c r="E89" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F89" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G89" s="6" t="s">
-        <v>91</v>
+        <v>126</v>
       </c>
       <c r="H89" s="2"/>
       <c r="I89" s="2" t="n">
         <v>70051000</v>
       </c>
       <c r="J89" s="2" t="s">
-        <v>87</v>
+        <v>122</v>
       </c>
       <c r="K89" s="6" t="s">
-        <v>104</v>
+        <v>139</v>
       </c>
       <c r="L89" s="6" t="s">
         <v>29</v>
@@ -5647,30 +6192,30 @@
       <c r="B90" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="C90" s="14" t="n">
+      <c r="C90" s="17" t="n">
         <v>46203</v>
       </c>
-      <c r="D90" s="14" t="n">
+      <c r="D90" s="17" t="n">
         <v>46203</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F90" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>91</v>
+        <v>126</v>
       </c>
       <c r="H90" s="2"/>
       <c r="I90" s="2" t="n">
         <v>42910311</v>
       </c>
       <c r="J90" s="2" t="s">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="K90" s="6" t="s">
-        <v>105</v>
+        <v>140</v>
       </c>
       <c r="L90" s="6" t="s">
         <v>19</v>
@@ -5689,30 +6234,30 @@
       <c r="B91" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="C91" s="14" t="n">
+      <c r="C91" s="17" t="n">
         <v>46203</v>
       </c>
-      <c r="D91" s="14" t="n">
+      <c r="D91" s="17" t="n">
         <v>46203</v>
       </c>
       <c r="E91" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F91" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G91" s="6" t="s">
-        <v>91</v>
+        <v>126</v>
       </c>
       <c r="H91" s="2"/>
       <c r="I91" s="2" t="n">
         <v>42910311</v>
       </c>
       <c r="J91" s="2" t="s">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="K91" s="6" t="s">
-        <v>106</v>
+        <v>141</v>
       </c>
       <c r="L91" s="6" t="s">
         <v>19</v>
@@ -5731,30 +6276,30 @@
       <c r="B92" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="C92" s="14" t="n">
+      <c r="C92" s="17" t="n">
         <v>46203</v>
       </c>
-      <c r="D92" s="14" t="n">
+      <c r="D92" s="17" t="n">
         <v>46203</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F92" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>91</v>
+        <v>126</v>
       </c>
       <c r="H92" s="2"/>
       <c r="I92" s="2" t="n">
         <v>68063200</v>
       </c>
       <c r="J92" s="2" t="s">
-        <v>90</v>
+        <v>125</v>
       </c>
       <c r="K92" s="6" t="s">
-        <v>105</v>
+        <v>140</v>
       </c>
       <c r="L92" s="6" t="s">
         <v>19</v>
@@ -5773,30 +6318,30 @@
       <c r="B93" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="C93" s="14" t="n">
+      <c r="C93" s="17" t="n">
         <v>46203</v>
       </c>
-      <c r="D93" s="14" t="n">
+      <c r="D93" s="17" t="n">
         <v>46203</v>
       </c>
       <c r="E93" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F93" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G93" s="6" t="s">
-        <v>91</v>
+        <v>126</v>
       </c>
       <c r="H93" s="2"/>
       <c r="I93" s="2" t="n">
         <v>70051000</v>
       </c>
       <c r="J93" s="2" t="s">
-        <v>87</v>
+        <v>122</v>
       </c>
       <c r="K93" s="6" t="s">
-        <v>106</v>
+        <v>141</v>
       </c>
       <c r="L93" s="6" t="s">
         <v>19</v>
@@ -5815,30 +6360,30 @@
       <c r="B94" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="C94" s="14" t="n">
+      <c r="C94" s="17" t="n">
         <v>46234</v>
       </c>
-      <c r="D94" s="14" t="n">
+      <c r="D94" s="17" t="n">
         <v>46234</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F94" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="H94" s="2"/>
       <c r="I94" s="2" t="n">
         <v>38160000</v>
       </c>
       <c r="J94" s="2" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="K94" s="6" t="s">
-        <v>99</v>
+        <v>134</v>
       </c>
       <c r="L94" s="6" t="s">
         <v>19</v>
@@ -5857,30 +6402,30 @@
       <c r="B95" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="C95" s="14" t="n">
+      <c r="C95" s="17" t="n">
         <v>46234</v>
       </c>
-      <c r="D95" s="14" t="n">
+      <c r="D95" s="17" t="n">
         <v>46234</v>
       </c>
       <c r="E95" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F95" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G95" s="6" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="H95" s="2"/>
       <c r="I95" s="2" t="n">
         <v>62100747</v>
       </c>
       <c r="J95" s="2" t="s">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="K95" s="6" t="s">
-        <v>99</v>
+        <v>134</v>
       </c>
       <c r="L95" s="6" t="s">
         <v>19</v>
@@ -5899,30 +6444,30 @@
       <c r="B96" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="C96" s="14" t="n">
+      <c r="C96" s="17" t="n">
         <v>46295</v>
       </c>
-      <c r="D96" s="14" t="n">
+      <c r="D96" s="17" t="n">
         <v>46295</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F96" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>107</v>
+        <v>142</v>
       </c>
       <c r="H96" s="2"/>
       <c r="I96" s="2" t="n">
         <v>38160000</v>
       </c>
       <c r="J96" s="2" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="K96" s="6" t="s">
-        <v>108</v>
+        <v>143</v>
       </c>
       <c r="L96" s="6" t="s">
         <v>23</v>
@@ -5941,30 +6486,30 @@
       <c r="B97" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="C97" s="14" t="n">
+      <c r="C97" s="17" t="n">
         <v>46295</v>
       </c>
-      <c r="D97" s="14" t="n">
+      <c r="D97" s="17" t="n">
         <v>46295</v>
       </c>
       <c r="E97" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F97" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G97" s="6" t="s">
-        <v>107</v>
+        <v>142</v>
       </c>
       <c r="H97" s="2"/>
       <c r="I97" s="2" t="n">
         <v>42910311</v>
       </c>
       <c r="J97" s="2" t="s">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="K97" s="6" t="s">
-        <v>109</v>
+        <v>144</v>
       </c>
       <c r="L97" s="6" t="s">
         <v>23</v>
@@ -5983,30 +6528,30 @@
       <c r="B98" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="C98" s="14" t="n">
+      <c r="C98" s="17" t="n">
         <v>46295</v>
       </c>
-      <c r="D98" s="14" t="n">
+      <c r="D98" s="17" t="n">
         <v>46295</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F98" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>107</v>
+        <v>142</v>
       </c>
       <c r="H98" s="2"/>
       <c r="I98" s="2" t="n">
         <v>42910311</v>
       </c>
       <c r="J98" s="2" t="s">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="K98" s="6" t="s">
-        <v>106</v>
+        <v>141</v>
       </c>
       <c r="L98" s="6" t="s">
         <v>19</v>
@@ -6025,30 +6570,30 @@
       <c r="B99" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="C99" s="14" t="n">
+      <c r="C99" s="17" t="n">
         <v>46295</v>
       </c>
-      <c r="D99" s="14" t="n">
+      <c r="D99" s="17" t="n">
         <v>46295</v>
       </c>
       <c r="E99" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F99" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G99" s="6" t="s">
-        <v>107</v>
+        <v>142</v>
       </c>
       <c r="H99" s="2"/>
       <c r="I99" s="2" t="n">
         <v>70051000</v>
       </c>
       <c r="J99" s="2" t="s">
-        <v>87</v>
+        <v>122</v>
       </c>
       <c r="K99" s="6" t="s">
-        <v>110</v>
+        <v>145</v>
       </c>
       <c r="L99" s="6" t="s">
         <v>23</v>
@@ -6067,30 +6612,30 @@
       <c r="B100" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="C100" s="14" t="n">
+      <c r="C100" s="17" t="n">
         <v>46295</v>
       </c>
-      <c r="D100" s="14" t="n">
+      <c r="D100" s="17" t="n">
         <v>46295</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F100" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>107</v>
+        <v>142</v>
       </c>
       <c r="H100" s="2"/>
       <c r="I100" s="2" t="n">
         <v>70051000</v>
       </c>
       <c r="J100" s="2" t="s">
-        <v>87</v>
+        <v>122</v>
       </c>
       <c r="K100" s="6" t="s">
-        <v>109</v>
+        <v>144</v>
       </c>
       <c r="L100" s="6" t="s">
         <v>23</v>
@@ -6109,30 +6654,30 @@
       <c r="B101" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="C101" s="14" t="n">
+      <c r="C101" s="17" t="n">
         <v>46295</v>
       </c>
-      <c r="D101" s="14" t="n">
+      <c r="D101" s="17" t="n">
         <v>46295</v>
       </c>
       <c r="E101" s="6" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F101" s="6" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G101" s="6" t="s">
-        <v>107</v>
+        <v>142</v>
       </c>
       <c r="H101" s="2"/>
       <c r="I101" s="2" t="n">
         <v>70051000</v>
       </c>
       <c r="J101" s="2" t="s">
-        <v>87</v>
+        <v>122</v>
       </c>
       <c r="K101" s="6" t="s">
-        <v>106</v>
+        <v>141</v>
       </c>
       <c r="L101" s="6" t="s">
         <v>19</v>
@@ -6157,7 +6702,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -6176,29 +6721,29 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="B1" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="C1" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="D1" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="F1" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="G1" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="H1" s="13" t="s">
-        <v>112</v>
+      <c r="A1" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="E1" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="F1" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="G1" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="H1" s="18" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6208,20 +6753,20 @@
       <c r="B2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="14" t="n">
+      <c r="C2" s="17" t="n">
         <v>46031</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>113</v>
+        <v>148</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>114</v>
+        <v>149</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>115</v>
+        <v>150</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>116</v>
+        <v>151</v>
       </c>
       <c r="H2" s="7" t="n">
         <v>669656093</v>
@@ -6234,20 +6779,20 @@
       <c r="B3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="14" t="n">
+      <c r="C3" s="17" t="n">
         <v>46031</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>113</v>
+        <v>148</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>114</v>
+        <v>149</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>115</v>
+        <v>150</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>116</v>
+        <v>151</v>
       </c>
       <c r="H3" s="7" t="n">
         <v>201128684</v>
@@ -6260,20 +6805,20 @@
       <c r="B4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="14" t="n">
+      <c r="C4" s="17" t="n">
         <v>46031</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>113</v>
+        <v>148</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>114</v>
+        <v>149</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>115</v>
+        <v>150</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>116</v>
+        <v>151</v>
       </c>
       <c r="H4" s="7" t="n">
         <v>1355026284</v>
@@ -6286,20 +6831,20 @@
       <c r="B5" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="14" t="n">
+      <c r="C5" s="17" t="n">
         <v>46031</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>113</v>
+        <v>148</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>114</v>
+        <v>149</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>115</v>
+        <v>150</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>116</v>
+        <v>151</v>
       </c>
       <c r="H5" s="7" t="n">
         <v>139366409</v>
@@ -6312,20 +6857,20 @@
       <c r="B6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="14" t="n">
+      <c r="C6" s="17" t="n">
         <v>46031</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>113</v>
+        <v>148</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>114</v>
+        <v>149</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>115</v>
+        <v>150</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>116</v>
+        <v>151</v>
       </c>
       <c r="H6" s="7" t="n">
         <v>732377864</v>
@@ -6338,20 +6883,20 @@
       <c r="B7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="14" t="n">
+      <c r="C7" s="17" t="n">
         <v>46031</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>113</v>
+        <v>148</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>114</v>
+        <v>149</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>115</v>
+        <v>150</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>116</v>
+        <v>151</v>
       </c>
       <c r="H7" s="7" t="n">
         <v>637997113</v>
@@ -6364,20 +6909,20 @@
       <c r="B8" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="14" t="n">
+      <c r="C8" s="17" t="n">
         <v>46034</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>117</v>
+        <v>152</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>118</v>
+        <v>153</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>119</v>
+        <v>154</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>120</v>
+        <v>155</v>
       </c>
       <c r="H8" s="7" t="n">
         <v>194099242</v>
@@ -6390,20 +6935,20 @@
       <c r="B9" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C9" s="14" t="n">
+      <c r="C9" s="17" t="n">
         <v>46034</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>117</v>
+        <v>152</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>118</v>
+        <v>153</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>119</v>
+        <v>154</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>120</v>
+        <v>155</v>
       </c>
       <c r="H9" s="7" t="n">
         <v>1313212538</v>
@@ -6416,20 +6961,20 @@
       <c r="B10" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C10" s="14" t="n">
+      <c r="C10" s="17" t="n">
         <v>46034</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>117</v>
+        <v>152</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>118</v>
+        <v>153</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>119</v>
+        <v>154</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>120</v>
+        <v>155</v>
       </c>
       <c r="H10" s="7" t="n">
         <v>292240228</v>
@@ -6442,20 +6987,20 @@
       <c r="B11" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="14" t="n">
+      <c r="C11" s="17" t="n">
         <v>46034</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>117</v>
+        <v>152</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>118</v>
+        <v>153</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>119</v>
+        <v>154</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>120</v>
+        <v>155</v>
       </c>
       <c r="H11" s="7" t="n">
         <v>240492525</v>
@@ -6468,20 +7013,20 @@
       <c r="B12" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C12" s="14" t="n">
+      <c r="C12" s="17" t="n">
         <v>46034</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>117</v>
+        <v>152</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>118</v>
+        <v>153</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>119</v>
+        <v>154</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>120</v>
+        <v>155</v>
       </c>
       <c r="H12" s="7" t="n">
         <v>1851555922</v>
@@ -6494,20 +7039,20 @@
       <c r="B13" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C13" s="14" t="n">
+      <c r="C13" s="17" t="n">
         <v>46034</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>117</v>
+        <v>152</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>118</v>
+        <v>153</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>119</v>
+        <v>154</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>120</v>
+        <v>155</v>
       </c>
       <c r="H13" s="7" t="n">
         <v>767113411</v>
@@ -6520,20 +7065,20 @@
       <c r="B14" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="14" t="n">
+      <c r="C14" s="17" t="n">
         <v>46034</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>117</v>
+        <v>152</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>118</v>
+        <v>153</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>119</v>
+        <v>154</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>120</v>
+        <v>155</v>
       </c>
       <c r="H14" s="7" t="n">
         <v>632116008</v>
@@ -6546,20 +7091,20 @@
       <c r="B15" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C15" s="14" t="n">
+      <c r="C15" s="17" t="n">
         <v>46058</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>117</v>
+        <v>152</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>121</v>
+        <v>156</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>119</v>
+        <v>154</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>120</v>
+        <v>155</v>
       </c>
       <c r="H15" s="7" t="n">
         <v>773240036</v>
@@ -6572,20 +7117,20 @@
       <c r="B16" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C16" s="14" t="n">
+      <c r="C16" s="17" t="n">
         <v>46140</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>122</v>
+        <v>157</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>123</v>
+        <v>158</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>115</v>
+        <v>150</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>124</v>
+        <v>159</v>
       </c>
       <c r="H16" s="7" t="n">
         <v>-554771272</v>
@@ -6598,20 +7143,20 @@
       <c r="B17" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C17" s="14" t="n">
+      <c r="C17" s="17" t="n">
         <v>46140</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>113</v>
+        <v>148</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>123</v>
+        <v>158</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>115</v>
+        <v>150</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>124</v>
+        <v>159</v>
       </c>
       <c r="H17" s="7" t="n">
         <v>554771272</v>
@@ -6624,20 +7169,20 @@
       <c r="B18" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C18" s="14" t="n">
+      <c r="C18" s="17" t="n">
         <v>46140</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>113</v>
+        <v>148</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>123</v>
+        <v>158</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>115</v>
+        <v>150</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>124</v>
+        <v>159</v>
       </c>
       <c r="H18" s="7" t="n">
         <v>554771272</v>
@@ -6650,20 +7195,20 @@
       <c r="B19" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="C19" s="14" t="n">
+      <c r="C19" s="17" t="n">
         <v>46212</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>117</v>
+        <v>152</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>119</v>
+        <v>154</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="H19" s="7" t="n">
         <v>742500000</v>
@@ -6680,7 +7225,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>127</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>

--- a/deliverables/VRP_GL_rollforward.xlsx
+++ b/deliverables/VRP_GL_rollforward.xlsx
@@ -10,11 +10,12 @@
   <sheets>
     <sheet name="요약" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="회사자료 대사" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="분개상세" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="VRP 지급내역" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="전기말 VRP 대사" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="분개상세" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="VRP 지급내역" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">분개상세!$A$1:$N$101</definedName>
+    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">분개상세!$A$1:$N$101</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="917" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1034" uniqueCount="249">
   <si>
     <t xml:space="preserve">VRP 구조조정충당부채 GL 정리 (2026.01~09)</t>
   </si>
@@ -214,6 +215,9 @@
     <t xml:space="preserve">⑩ 9/30 퇴직 640,952,952원은 9월말 미지급(10월 지급 예정) → 9월말 '25 Drive 2 잔액 3,513,646,441원 중 자료로 설명되는 금액은 640,952,952원뿐이며 2,872,693,490원은 근거 없음(과다 계상 가능성). 11·12월 퇴직 예정 2건(Corporate Functions)은 금액 미기재 → '26 신규 959.5백만원의 근거 불충분. 시트 '회사자료 대사' 참조.</t>
   </si>
   <si>
+    <t xml:space="preserve">⑪ 전기말 자료(VRP_Accrual-Actual) 대사: 2025.12.31 퇴사 19명 Actual 9,020,449,323원 = 1월 사용 9,029,878,628원 + 2월 조정 -9,429,305원(CC 11개 모두 일치). 9월말 잔액 중 근거 없는 2,872.7백만원 = ① Accrual(29명) 미실현 중 미환입 1,547.3백만원 + ② 전기말 잔액 중 Accrual 외 금액 1,325.4백만원(2025.10말 기존 잔액 1,602.2백만원 이월분 추정). 시트 '전기말 VRP 대사' 참조.</t>
+  </si>
+  <si>
     <t xml:space="preserve">회사 VRP 자료(4.06_VRP_2026 'Simulation') vs GL 대사</t>
   </si>
   <si>
@@ -314,6 +318,261 @@
   </si>
   <si>
     <t xml:space="preserve">금액 미기재 → 산정 근거 요청</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전기말 VRP 자료(VRP_Accrual-Actual) vs GL 대사</t>
+  </si>
+  <si>
+    <t xml:space="preserve">회사자료: Accrual 시트(2025.9 시뮬레이션, 29명, 9월 환율 1,617.01) / Actual 시트(2025년 퇴사자 21명) / 2026 Simulation(2026년 퇴사 6건). GL: 2025년 월별 잔액은 BSPL2025, 2026년은 GL. 금액 원 단위.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 2025.12.31 퇴사자 19명: 회사 Actual vs 2026년 1월 충당부채 사용(120000018) + 2월 조정(120000055)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">인원</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Actual VRP(회사)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1월 사용</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2월 조정</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GL 사용 순액</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0000033250</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0000050101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0000053111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0000053212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0000053217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0000053313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0000053717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0000053721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0000053760</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0000066772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">주) 1월 실제 지급(급여대장 SE 5,290.8백만 + 연금사업자 KR 3,735.6백만 = 9,026.4백만)과 Actual 합계 차이 5.9백만원은 원천세·연금 정산 차이로 추정.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. 2025.9 Accrual(29명) vs 실제 퇴사(2025.12.31 19명 + 2026년 4명) - CC별</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accrual 인원</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accrual VRP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">실제 인원</t>
+  </si>
+  <si>
+    <t xml:space="preserve">실제 VRP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미실현(Accrual-실제)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0000050102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multaq Sales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DM Squad 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DM Squad 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0000053310</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DM2 Commerical lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oncology_squad 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026년 퇴사 포함</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oncology_squad 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oncology Marketing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oncology Commercial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Onco CE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0000066776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DM CE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diabetes Franchise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GenMed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transplant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accrual에 없는 CC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DM Squad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CV Squad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">주) 2026년 실제: 1/31 퇴사(66792) 773,240,036(2월 GL 지급), 4/30(53716) 552,383,939, 6/30(53799) 742,500,000, 9/30(53716) 640,952,952(미지급, 회사 추정액). Accrual은 계획 CC, Actual은 개인 CC 기준이라 CC 간 이동이 있음.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. 2025년 월별 충당부채 잔액 (BSPL2025, 대변 잔액)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025.06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025.08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025.11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025.12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11월 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38160000 VRP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11월 Drive 2 설정 / 12월 -342.2백만</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42910311 전직지원</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11월 +105백만(30명×3.5백만)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70051000 전입액(누적)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6월 기존 프로그램 834.9백만</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. 잔액 브릿지 ('25 Drive 2 VRP, 38160000)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">항목</t>
+  </si>
+  <si>
+    <t xml:space="preserve">금액</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025.12 GL 잔액</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSPL2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(-) Accrual VRP (29명)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">회사 Accrual 시트</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(=) Accrual 외 잔액 (10월말 기존잔액 1,602.2백만 등)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">근거 확인 필요</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accrual VRP (29명)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(-) 2025.12.31 퇴사 19명 사용</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1~2월</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(-) 2026년 퇴사 지급 3명 (1/31, 4/30, 6/30)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2·4·7월</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(-) 2026.9.30 퇴사 1명 (미지급)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9월말 잔액에 남아야 할 금액</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(=) Accrual 미실현</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(-) 3월 환입</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120000074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(=) Accrual 미실현 중 미환입</t>
+  </si>
+  <si>
+    <t xml:space="preserve">추가 환입 대상 여부 확인</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9월말 GL 잔액</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(=) 9/30 퇴사자 미지급</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+ Accrual 미실현 중 미환입</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+ Accrual 외 잔액</t>
   </si>
   <si>
     <t xml:space="preserve">전표번호</t>
@@ -985,7 +1244,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J54"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1983,8 +2242,22 @@
       <c r="I54" s="11"/>
       <c r="J54" s="11"/>
     </row>
+    <row r="55" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="B55" s="12"/>
+      <c r="C55" s="12"/>
+      <c r="D55" s="12"/>
+      <c r="E55" s="12"/>
+      <c r="F55" s="12"/>
+      <c r="G55" s="12"/>
+      <c r="H55" s="12"/>
+      <c r="I55" s="12"/>
+      <c r="J55" s="12"/>
+    </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A45:J45"/>
     <mergeCell ref="A46:J46"/>
     <mergeCell ref="A47:J47"/>
@@ -1995,6 +2268,7 @@
     <mergeCell ref="A52:J52"/>
     <mergeCell ref="A53:J53"/>
     <mergeCell ref="A54:J54"/>
+    <mergeCell ref="A55:J55"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2029,47 +2303,47 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H4" s="15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I4" s="16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J4" s="15" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2077,10 +2351,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D5" s="17" t="n">
         <v>46053</v>
@@ -2105,7 +2379,7 @@
         <v>773240036</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2113,10 +2387,10 @@
         <v>2</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D6" s="17" t="n">
         <v>46142</v>
@@ -2141,7 +2415,7 @@
         <v>554771272</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2149,10 +2423,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D7" s="17" t="n">
         <v>46203</v>
@@ -2177,7 +2451,7 @@
         <v>742500000</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2185,10 +2459,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D8" s="17" t="n">
         <v>46295</v>
@@ -2202,7 +2476,7 @@
       <c r="I8" s="7"/>
       <c r="J8" s="7"/>
       <c r="K8" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2210,24 +2484,24 @@
         <v>5</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D9" s="17" t="n">
         <v>46356</v>
       </c>
       <c r="E9" s="7"/>
       <c r="F9" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="7"/>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
       <c r="K9" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2235,24 +2509,24 @@
         <v>6</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D10" s="17" t="n">
         <v>46387</v>
       </c>
       <c r="E10" s="7"/>
       <c r="F10" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="7"/>
       <c r="I10" s="7"/>
       <c r="J10" s="7"/>
       <c r="K10" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2297,7 +2571,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -2312,7 +2586,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -2330,7 +2604,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -2348,7 +2622,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -2363,12 +2637,12 @@
       <c r="I16" s="7"/>
       <c r="J16" s="7"/>
       <c r="K16" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -2386,7 +2660,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -2400,7 +2674,7 @@
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
       <c r="K18" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -2415,6 +2689,1160 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:H65"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="40"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="13" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="B6" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>140158707.5</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>139366409</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>792299</v>
+      </c>
+      <c r="F6" s="7" t="n">
+        <f aca="false">D6+E6</f>
+        <v>140158708</v>
+      </c>
+      <c r="G6" s="7" t="n">
+        <f aca="false">C6-F6</f>
+        <v>-0.5</v>
+      </c>
+      <c r="H6" s="2"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="B7" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>194099242</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>194499104</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>-399862</v>
+      </c>
+      <c r="F7" s="7" t="n">
+        <f aca="false">D7+E7</f>
+        <v>194099242</v>
+      </c>
+      <c r="G7" s="7" t="n">
+        <f aca="false">C7-F7</f>
+        <v>0</v>
+      </c>
+      <c r="H7" s="2"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="B8" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>1313212538.42</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>1314748766</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>-1536228</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <f aca="false">D8+E8</f>
+        <v>1313212538</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <f aca="false">C8-F8</f>
+        <v>0.420000076293945</v>
+      </c>
+      <c r="H8" s="2"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B9" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>731433825.83</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>732377864</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>-944038</v>
+      </c>
+      <c r="F9" s="7" t="n">
+        <f aca="false">D9+E9</f>
+        <v>731433826</v>
+      </c>
+      <c r="G9" s="7" t="n">
+        <f aca="false">C9-F9</f>
+        <v>-0.169999957084656</v>
+      </c>
+      <c r="H9" s="2"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="B10" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>292240228</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>292240228</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="7" t="n">
+        <f aca="false">D10+E10</f>
+        <v>292240228</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <f aca="false">C10-F10</f>
+        <v>0</v>
+      </c>
+      <c r="H10" s="2"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="B11" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>637298272.78</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>637997113</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>-698840</v>
+      </c>
+      <c r="F11" s="7" t="n">
+        <f aca="false">D11+E11</f>
+        <v>637298273</v>
+      </c>
+      <c r="G11" s="7" t="n">
+        <f aca="false">C11-F11</f>
+        <v>-0.22000002861023</v>
+      </c>
+      <c r="H11" s="2"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B12" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>1593544566.88</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>1595518809</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>-1974242</v>
+      </c>
+      <c r="F12" s="7" t="n">
+        <f aca="false">D12+E12</f>
+        <v>1593544567</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <f aca="false">C12-F12</f>
+        <v>-0.119999885559082</v>
+      </c>
+      <c r="H12" s="2"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="B13" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" s="7" t="n">
+        <v>2518266072.62</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>2521212015</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>-2945943</v>
+      </c>
+      <c r="F13" s="7" t="n">
+        <f aca="false">D13+E13</f>
+        <v>2518266072</v>
+      </c>
+      <c r="G13" s="7" t="n">
+        <f aca="false">C13-F13</f>
+        <v>0.619999885559082</v>
+      </c>
+      <c r="H13" s="2"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="B14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="7" t="n">
+        <v>200966449.53</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>201128684</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>-162234</v>
+      </c>
+      <c r="F14" s="7" t="n">
+        <f aca="false">D14+E14</f>
+        <v>200966450</v>
+      </c>
+      <c r="G14" s="7" t="n">
+        <f aca="false">C14-F14</f>
+        <v>-0.469999998807907</v>
+      </c>
+      <c r="H14" s="2"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="B15" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" s="7" t="n">
+        <v>767113410.91</v>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>768016582</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>-903171</v>
+      </c>
+      <c r="F15" s="7" t="n">
+        <f aca="false">D15+E15</f>
+        <v>767113411</v>
+      </c>
+      <c r="G15" s="7" t="n">
+        <f aca="false">C15-F15</f>
+        <v>-0.0900000333786011</v>
+      </c>
+      <c r="H15" s="2"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B16" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" s="7" t="n">
+        <v>632116008.33</v>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>632773054</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>-657046</v>
+      </c>
+      <c r="F16" s="7" t="n">
+        <f aca="false">D16+E16</f>
+        <v>632116008</v>
+      </c>
+      <c r="G16" s="7" t="n">
+        <f aca="false">C16-F16</f>
+        <v>0.330000042915344</v>
+      </c>
+      <c r="H16" s="2"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="9" t="n">
+        <f aca="false">SUM(B6:B16)</f>
+        <v>19</v>
+      </c>
+      <c r="C17" s="9" t="n">
+        <f aca="false">SUM(C6:C16)</f>
+        <v>9020449322.8</v>
+      </c>
+      <c r="D17" s="9" t="n">
+        <f aca="false">SUM(D6:D16)</f>
+        <v>9029878628</v>
+      </c>
+      <c r="E17" s="9" t="n">
+        <f aca="false">SUM(E6:E16)</f>
+        <v>-9429305</v>
+      </c>
+      <c r="F17" s="9" t="n">
+        <f aca="false">SUM(F6:F16)</f>
+        <v>9020449323</v>
+      </c>
+      <c r="G17" s="9" t="n">
+        <f aca="false">SUM(G6:G16)</f>
+        <v>-0.199999898672104</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="C22" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>593473154.5</v>
+      </c>
+      <c r="E22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="7" t="n">
+        <f aca="false">D22-F22</f>
+        <v>593473154.5</v>
+      </c>
+      <c r="H22" s="2"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="C23" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>4767905162.04</v>
+      </c>
+      <c r="E23" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="7" t="n">
+        <v>731433825.83</v>
+      </c>
+      <c r="G23" s="7" t="n">
+        <f aca="false">D23-F23</f>
+        <v>4036471336.21</v>
+      </c>
+      <c r="H23" s="2"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="C24" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>1036279187.06</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="7" t="n">
+        <v>292240228</v>
+      </c>
+      <c r="G24" s="7" t="n">
+        <f aca="false">D24-F24</f>
+        <v>744038959.06</v>
+      </c>
+      <c r="H24" s="2"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="C25" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="7" t="n">
+        <v>661519760.5</v>
+      </c>
+      <c r="E25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="7" t="n">
+        <f aca="false">D25-F25</f>
+        <v>661519760.5</v>
+      </c>
+      <c r="H25" s="2"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="C26" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>2090342673.8</v>
+      </c>
+      <c r="E26" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F26" s="7" t="n">
+        <v>2786881457.38</v>
+      </c>
+      <c r="G26" s="7" t="n">
+        <f aca="false">D26-F26</f>
+        <v>-696538783.58</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="C27" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>2590377472.55</v>
+      </c>
+      <c r="E27" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F27" s="7" t="n">
+        <v>2518266072.62</v>
+      </c>
+      <c r="G27" s="7" t="n">
+        <f aca="false">D27-F27</f>
+        <v>72111399.9300003</v>
+      </c>
+      <c r="H27" s="2"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="C28" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>745304630.75</v>
+      </c>
+      <c r="E28" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F28" s="7" t="n">
+        <v>767113410.91</v>
+      </c>
+      <c r="G28" s="7" t="n">
+        <f aca="false">D28-F28</f>
+        <v>-21808780.16</v>
+      </c>
+      <c r="H28" s="2"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="C29" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="7" t="n">
+        <v>720530632</v>
+      </c>
+      <c r="E29" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" s="7" t="n">
+        <v>742500000</v>
+      </c>
+      <c r="G29" s="7" t="n">
+        <f aca="false">D29-F29</f>
+        <v>-21969368</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="C30" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="7" t="n">
+        <v>612622990</v>
+      </c>
+      <c r="E30" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" s="7" t="n">
+        <v>632116008.33</v>
+      </c>
+      <c r="G30" s="7" t="n">
+        <f aca="false">D30-F30</f>
+        <v>-19493018.33</v>
+      </c>
+      <c r="H30" s="2"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="C31" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" s="7" t="n">
+        <v>525381150.94</v>
+      </c>
+      <c r="E31" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="7" t="n">
+        <f aca="false">D31-F31</f>
+        <v>525381150.94</v>
+      </c>
+      <c r="H31" s="2"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="C32" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="7" t="n">
+        <v>751181126.5</v>
+      </c>
+      <c r="E32" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="7" t="n">
+        <v>773240036</v>
+      </c>
+      <c r="G32" s="7" t="n">
+        <f aca="false">D32-F32</f>
+        <v>-22058909.5</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="C33" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="7" t="n">
+        <v>453223623.35</v>
+      </c>
+      <c r="E33" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="7" t="n">
+        <v>140158707.5</v>
+      </c>
+      <c r="G33" s="7" t="n">
+        <f aca="false">D33-F33</f>
+        <v>313064915.85</v>
+      </c>
+      <c r="H33" s="2"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="C34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" s="7" t="n">
+        <v>194099242</v>
+      </c>
+      <c r="G34" s="7" t="n">
+        <f aca="false">D34-F34</f>
+        <v>-194099242</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="C35" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F35" s="7" t="n">
+        <v>1313212538.42</v>
+      </c>
+      <c r="G35" s="7" t="n">
+        <f aca="false">D35-F35</f>
+        <v>-1313212538.42</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="C36" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" s="7" t="n">
+        <v>637298272.78</v>
+      </c>
+      <c r="G36" s="7" t="n">
+        <f aca="false">D36-F36</f>
+        <v>-637298272.78</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="C37" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" s="7" t="n">
+        <v>200966449.53</v>
+      </c>
+      <c r="G37" s="7" t="n">
+        <f aca="false">D37-F37</f>
+        <v>-200966449.53</v>
+      </c>
+      <c r="H37" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B38" s="3"/>
+      <c r="C38" s="9" t="n">
+        <f aca="false">SUM(C22:C37)</f>
+        <v>29</v>
+      </c>
+      <c r="D38" s="9" t="n">
+        <f aca="false">SUM(D22:D37)</f>
+        <v>15548141563.99</v>
+      </c>
+      <c r="E38" s="9" t="n">
+        <f aca="false">SUM(E22:E37)</f>
+        <v>23</v>
+      </c>
+      <c r="F38" s="9" t="n">
+        <f aca="false">SUM(F22:F37)</f>
+        <v>11729526249.3</v>
+      </c>
+      <c r="G38" s="9" t="n">
+        <f aca="false">SUM(G22:G37)</f>
+        <v>3818615314.69</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="F42" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="G42" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="B43" s="7" t="n">
+        <v>3331457110</v>
+      </c>
+      <c r="C43" s="7" t="n">
+        <v>1755088531</v>
+      </c>
+      <c r="D43" s="7" t="n">
+        <v>1602210232</v>
+      </c>
+      <c r="E43" s="7" t="n">
+        <v>17215763234</v>
+      </c>
+      <c r="F43" s="7" t="n">
+        <v>16873571611</v>
+      </c>
+      <c r="G43" s="7" t="n">
+        <f aca="false">E43-D43</f>
+        <v>15613553002</v>
+      </c>
+      <c r="H43" s="6" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="B44" s="7" t="n">
+        <v>21000000</v>
+      </c>
+      <c r="C44" s="7" t="n">
+        <v>21000000</v>
+      </c>
+      <c r="D44" s="7" t="n">
+        <v>21000000</v>
+      </c>
+      <c r="E44" s="7" t="n">
+        <v>126000000</v>
+      </c>
+      <c r="F44" s="7" t="n">
+        <v>122500000</v>
+      </c>
+      <c r="G44" s="7" t="n">
+        <f aca="false">E44-D44</f>
+        <v>105000000</v>
+      </c>
+      <c r="H44" s="6" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="B45" s="7" t="n">
+        <v>834930708</v>
+      </c>
+      <c r="C45" s="7" t="n">
+        <v>834930708</v>
+      </c>
+      <c r="D45" s="7" t="n">
+        <v>834930708</v>
+      </c>
+      <c r="E45" s="7" t="n">
+        <v>16905364104</v>
+      </c>
+      <c r="F45" s="7" t="n">
+        <v>16559672481</v>
+      </c>
+      <c r="G45" s="7" t="n">
+        <f aca="false">E45-D45</f>
+        <v>16070433396</v>
+      </c>
+      <c r="H45" s="6" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="B49" s="7" t="n">
+        <v>16873571611</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="B50" s="7" t="n">
+        <f aca="false">-D38</f>
+        <v>-15548141563.99</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="B51" s="7" t="n">
+        <f aca="false">B49+B50</f>
+        <v>1325430047.01</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="B53" s="7" t="n">
+        <f aca="false">D38</f>
+        <v>15548141563.99</v>
+      </c>
+      <c r="C53" s="2"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="B54" s="7" t="n">
+        <f aca="false">-F17</f>
+        <v>-9020449323</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="B55" s="7" t="n">
+        <v>-2068123975</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="B56" s="7" t="n">
+        <v>-640952951.5</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="B57" s="7" t="n">
+        <f aca="false">SUM(B53:B56)</f>
+        <v>3818615314.49</v>
+      </c>
+      <c r="C57" s="2"/>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B58" s="7" t="n">
+        <v>-2271351872</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="B59" s="7" t="n">
+        <f aca="false">B57+B58</f>
+        <v>1547263442.49</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="B61" s="7" t="n">
+        <f aca="false">-(-16873571611+SUMIFS(분개상세!$N$2:$N$101,분개상세!$I$2:$I$101,38160000,분개상세!$L$2:$L$101,"'25 Drive 2 (commercial)"))</f>
+        <v>3513646441</v>
+      </c>
+      <c r="C61" s="2"/>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="B62" s="7" t="n">
+        <v>640952951.5</v>
+      </c>
+      <c r="C62" s="2"/>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="B63" s="7" t="n">
+        <f aca="false">B59</f>
+        <v>1547263442.49</v>
+      </c>
+      <c r="C63" s="2"/>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="B64" s="7" t="n">
+        <f aca="false">B51</f>
+        <v>1325430047.01</v>
+      </c>
+      <c r="C64" s="2"/>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B65" s="9" t="n">
+        <f aca="false">B61-B62-B63-B64</f>
+        <v>0</v>
+      </c>
+      <c r="C65" s="3"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -2439,46 +3867,46 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="18" t="s">
-        <v>96</v>
+        <v>182</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>97</v>
+        <v>183</v>
       </c>
       <c r="C1" s="18" t="s">
-        <v>98</v>
+        <v>184</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>99</v>
+        <v>185</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>100</v>
+        <v>186</v>
       </c>
       <c r="F1" s="18" t="s">
-        <v>101</v>
+        <v>187</v>
       </c>
       <c r="G1" s="18" t="s">
-        <v>102</v>
+        <v>188</v>
       </c>
       <c r="H1" s="18" t="s">
-        <v>103</v>
+        <v>189</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>104</v>
+        <v>190</v>
       </c>
       <c r="J1" s="18" t="s">
-        <v>105</v>
+        <v>191</v>
       </c>
       <c r="K1" s="18" t="s">
-        <v>106</v>
+        <v>192</v>
       </c>
       <c r="L1" s="18" t="s">
         <v>17</v>
       </c>
       <c r="M1" s="18" t="s">
-        <v>107</v>
+        <v>193</v>
       </c>
       <c r="N1" s="18" t="s">
-        <v>108</v>
+        <v>194</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2495,10 +3923,10 @@
         <v>46022</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>109</v>
+        <v>195</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="n">
@@ -2508,14 +3936,14 @@
         <v>38160000</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>111</v>
+        <v>197</v>
       </c>
       <c r="K2" s="2"/>
       <c r="L2" s="2" t="s">
         <v>30</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>112</v>
+        <v>198</v>
       </c>
       <c r="N2" s="7" t="n">
         <v>1228771976</v>
@@ -2535,10 +3963,10 @@
         <v>46022</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>109</v>
+        <v>195</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2" t="n">
@@ -2548,14 +3976,14 @@
         <v>38160000</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>111</v>
+        <v>197</v>
       </c>
       <c r="K3" s="2"/>
       <c r="L3" s="2" t="s">
         <v>30</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>112</v>
+        <v>198</v>
       </c>
       <c r="N3" s="7" t="n">
         <v>-14455123</v>
@@ -2575,10 +4003,10 @@
         <v>46022</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>109</v>
+        <v>195</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2" t="n">
@@ -2588,14 +4016,14 @@
         <v>38160000</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>111</v>
+        <v>197</v>
       </c>
       <c r="K4" s="2"/>
       <c r="L4" s="2" t="s">
         <v>30</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>112</v>
+        <v>198</v>
       </c>
       <c r="N4" s="7" t="n">
         <v>-954316853</v>
@@ -2615,10 +4043,10 @@
         <v>46022</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>109</v>
+        <v>195</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2" t="n">
@@ -2628,14 +4056,14 @@
         <v>38160000</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>111</v>
+        <v>197</v>
       </c>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
         <v>30</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>112</v>
+        <v>198</v>
       </c>
       <c r="N5" s="7" t="n">
         <v>-260000000</v>
@@ -2655,23 +4083,23 @@
         <v>46053</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>114</v>
+        <v>200</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2" t="n">
         <v>38160000</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>111</v>
+        <v>197</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>115</v>
+        <v>201</v>
       </c>
       <c r="L6" s="6" t="s">
         <v>19</v>
@@ -2697,23 +4125,23 @@
         <v>46053</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>114</v>
+        <v>200</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2" t="n">
         <v>38160000</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>111</v>
+        <v>197</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>115</v>
+        <v>201</v>
       </c>
       <c r="L7" s="6" t="s">
         <v>19</v>
@@ -2739,23 +4167,23 @@
         <v>46053</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>114</v>
+        <v>200</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2" t="n">
         <v>38160000</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>111</v>
+        <v>197</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>115</v>
+        <v>201</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>19</v>
@@ -2781,23 +4209,23 @@
         <v>46053</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>114</v>
+        <v>200</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2" t="n">
         <v>38160000</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>111</v>
+        <v>197</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>115</v>
+        <v>201</v>
       </c>
       <c r="L9" s="6" t="s">
         <v>19</v>
@@ -2823,23 +4251,23 @@
         <v>46053</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>114</v>
+        <v>200</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2" t="n">
         <v>38160000</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>111</v>
+        <v>197</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>115</v>
+        <v>201</v>
       </c>
       <c r="L10" s="6" t="s">
         <v>19</v>
@@ -2865,23 +4293,23 @@
         <v>46053</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>114</v>
+        <v>200</v>
       </c>
       <c r="H11" s="2"/>
       <c r="I11" s="2" t="n">
         <v>38160000</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>111</v>
+        <v>197</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>115</v>
+        <v>201</v>
       </c>
       <c r="L11" s="6" t="s">
         <v>19</v>
@@ -2907,23 +4335,23 @@
         <v>46053</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>114</v>
+        <v>200</v>
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="2" t="n">
         <v>38160000</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>111</v>
+        <v>197</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>115</v>
+        <v>201</v>
       </c>
       <c r="L12" s="6" t="s">
         <v>19</v>
@@ -2949,23 +4377,23 @@
         <v>46053</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>114</v>
+        <v>200</v>
       </c>
       <c r="H13" s="2"/>
       <c r="I13" s="2" t="n">
         <v>38160000</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>111</v>
+        <v>197</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>115</v>
+        <v>201</v>
       </c>
       <c r="L13" s="6" t="s">
         <v>19</v>
@@ -2991,23 +4419,23 @@
         <v>46053</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>114</v>
+        <v>200</v>
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="2" t="n">
         <v>38160000</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>111</v>
+        <v>197</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>115</v>
+        <v>201</v>
       </c>
       <c r="L14" s="6" t="s">
         <v>19</v>
@@ -3033,23 +4461,23 @@
         <v>46053</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>114</v>
+        <v>200</v>
       </c>
       <c r="H15" s="2"/>
       <c r="I15" s="2" t="n">
         <v>38160000</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>111</v>
+        <v>197</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>115</v>
+        <v>201</v>
       </c>
       <c r="L15" s="6" t="s">
         <v>19</v>
@@ -3075,23 +4503,23 @@
         <v>46053</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>114</v>
+        <v>200</v>
       </c>
       <c r="H16" s="2"/>
       <c r="I16" s="2" t="n">
         <v>38160000</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>111</v>
+        <v>197</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>115</v>
+        <v>201</v>
       </c>
       <c r="L16" s="6" t="s">
         <v>19</v>
@@ -3117,23 +4545,23 @@
         <v>46053</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>114</v>
+        <v>200</v>
       </c>
       <c r="H17" s="2"/>
       <c r="I17" s="2" t="n">
         <v>62100747</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>116</v>
+        <v>202</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>115</v>
+        <v>201</v>
       </c>
       <c r="L17" s="6" t="s">
         <v>19</v>
@@ -3159,23 +4587,23 @@
         <v>46053</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>114</v>
+        <v>200</v>
       </c>
       <c r="H18" s="2"/>
       <c r="I18" s="2" t="n">
         <v>62100747</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>116</v>
+        <v>202</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>115</v>
+        <v>201</v>
       </c>
       <c r="L18" s="6" t="s">
         <v>19</v>
@@ -3201,23 +4629,23 @@
         <v>46053</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>114</v>
+        <v>200</v>
       </c>
       <c r="H19" s="2"/>
       <c r="I19" s="2" t="n">
         <v>62100747</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>116</v>
+        <v>202</v>
       </c>
       <c r="K19" s="6" t="s">
-        <v>115</v>
+        <v>201</v>
       </c>
       <c r="L19" s="6" t="s">
         <v>19</v>
@@ -3243,23 +4671,23 @@
         <v>46053</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>114</v>
+        <v>200</v>
       </c>
       <c r="H20" s="2"/>
       <c r="I20" s="2" t="n">
         <v>62100747</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>116</v>
+        <v>202</v>
       </c>
       <c r="K20" s="6" t="s">
-        <v>115</v>
+        <v>201</v>
       </c>
       <c r="L20" s="6" t="s">
         <v>19</v>
@@ -3285,23 +4713,23 @@
         <v>46053</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>114</v>
+        <v>200</v>
       </c>
       <c r="H21" s="2"/>
       <c r="I21" s="2" t="n">
         <v>62100747</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>116</v>
+        <v>202</v>
       </c>
       <c r="K21" s="6" t="s">
-        <v>115</v>
+        <v>201</v>
       </c>
       <c r="L21" s="6" t="s">
         <v>19</v>
@@ -3327,23 +4755,23 @@
         <v>46053</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>114</v>
+        <v>200</v>
       </c>
       <c r="H22" s="2"/>
       <c r="I22" s="2" t="n">
         <v>62100747</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>116</v>
+        <v>202</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>115</v>
+        <v>201</v>
       </c>
       <c r="L22" s="6" t="s">
         <v>19</v>
@@ -3369,23 +4797,23 @@
         <v>46053</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>114</v>
+        <v>200</v>
       </c>
       <c r="H23" s="2"/>
       <c r="I23" s="2" t="n">
         <v>62100747</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>116</v>
+        <v>202</v>
       </c>
       <c r="K23" s="6" t="s">
-        <v>115</v>
+        <v>201</v>
       </c>
       <c r="L23" s="6" t="s">
         <v>19</v>
@@ -3411,23 +4839,23 @@
         <v>46053</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>114</v>
+        <v>200</v>
       </c>
       <c r="H24" s="2"/>
       <c r="I24" s="2" t="n">
         <v>62100747</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>116</v>
+        <v>202</v>
       </c>
       <c r="K24" s="6" t="s">
-        <v>115</v>
+        <v>201</v>
       </c>
       <c r="L24" s="6" t="s">
         <v>19</v>
@@ -3453,23 +4881,23 @@
         <v>46053</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>114</v>
+        <v>200</v>
       </c>
       <c r="H25" s="2"/>
       <c r="I25" s="2" t="n">
         <v>62100747</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>116</v>
+        <v>202</v>
       </c>
       <c r="K25" s="6" t="s">
-        <v>115</v>
+        <v>201</v>
       </c>
       <c r="L25" s="6" t="s">
         <v>19</v>
@@ -3495,23 +4923,23 @@
         <v>46053</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>114</v>
+        <v>200</v>
       </c>
       <c r="H26" s="2"/>
       <c r="I26" s="2" t="n">
         <v>62100747</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>116</v>
+        <v>202</v>
       </c>
       <c r="K26" s="6" t="s">
-        <v>115</v>
+        <v>201</v>
       </c>
       <c r="L26" s="6" t="s">
         <v>19</v>
@@ -3537,23 +4965,23 @@
         <v>46053</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>114</v>
+        <v>200</v>
       </c>
       <c r="H27" s="2"/>
       <c r="I27" s="2" t="n">
         <v>62100747</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>116</v>
+        <v>202</v>
       </c>
       <c r="K27" s="6" t="s">
-        <v>115</v>
+        <v>201</v>
       </c>
       <c r="L27" s="6" t="s">
         <v>19</v>
@@ -3579,23 +5007,23 @@
         <v>46081</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>114</v>
+        <v>200</v>
       </c>
       <c r="H28" s="2"/>
       <c r="I28" s="2" t="n">
         <v>38160000</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>111</v>
+        <v>197</v>
       </c>
       <c r="K28" s="6" t="s">
-        <v>117</v>
+        <v>203</v>
       </c>
       <c r="L28" s="6" t="s">
         <v>19</v>
@@ -3621,23 +5049,23 @@
         <v>46081</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>114</v>
+        <v>200</v>
       </c>
       <c r="H29" s="2"/>
       <c r="I29" s="2" t="n">
         <v>38160000</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>111</v>
+        <v>197</v>
       </c>
       <c r="K29" s="6" t="s">
-        <v>117</v>
+        <v>203</v>
       </c>
       <c r="L29" s="6" t="s">
         <v>19</v>
@@ -3663,23 +5091,23 @@
         <v>46081</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>114</v>
+        <v>200</v>
       </c>
       <c r="H30" s="2"/>
       <c r="I30" s="2" t="n">
         <v>38160000</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>111</v>
+        <v>197</v>
       </c>
       <c r="K30" s="6" t="s">
-        <v>117</v>
+        <v>203</v>
       </c>
       <c r="L30" s="6" t="s">
         <v>19</v>
@@ -3705,23 +5133,23 @@
         <v>46081</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>114</v>
+        <v>200</v>
       </c>
       <c r="H31" s="2"/>
       <c r="I31" s="2" t="n">
         <v>38160000</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>111</v>
+        <v>197</v>
       </c>
       <c r="K31" s="6" t="s">
-        <v>117</v>
+        <v>203</v>
       </c>
       <c r="L31" s="6" t="s">
         <v>19</v>
@@ -3747,23 +5175,23 @@
         <v>46081</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>114</v>
+        <v>200</v>
       </c>
       <c r="H32" s="2"/>
       <c r="I32" s="2" t="n">
         <v>38160000</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>111</v>
+        <v>197</v>
       </c>
       <c r="K32" s="6" t="s">
-        <v>117</v>
+        <v>203</v>
       </c>
       <c r="L32" s="6" t="s">
         <v>19</v>
@@ -3789,23 +5217,23 @@
         <v>46081</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>114</v>
+        <v>200</v>
       </c>
       <c r="H33" s="2"/>
       <c r="I33" s="2" t="n">
         <v>38160000</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>111</v>
+        <v>197</v>
       </c>
       <c r="K33" s="6" t="s">
-        <v>117</v>
+        <v>203</v>
       </c>
       <c r="L33" s="6" t="s">
         <v>19</v>
@@ -3831,23 +5259,23 @@
         <v>46081</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>114</v>
+        <v>200</v>
       </c>
       <c r="H34" s="2"/>
       <c r="I34" s="2" t="n">
         <v>38160000</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>111</v>
+        <v>197</v>
       </c>
       <c r="K34" s="6" t="s">
-        <v>117</v>
+        <v>203</v>
       </c>
       <c r="L34" s="6" t="s">
         <v>19</v>
@@ -3873,23 +5301,23 @@
         <v>46081</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>114</v>
+        <v>200</v>
       </c>
       <c r="H35" s="2"/>
       <c r="I35" s="2" t="n">
         <v>38160000</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>111</v>
+        <v>197</v>
       </c>
       <c r="K35" s="6" t="s">
-        <v>117</v>
+        <v>203</v>
       </c>
       <c r="L35" s="6" t="s">
         <v>19</v>
@@ -3915,23 +5343,23 @@
         <v>46081</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>114</v>
+        <v>200</v>
       </c>
       <c r="H36" s="2"/>
       <c r="I36" s="2" t="n">
         <v>38160000</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>111</v>
+        <v>197</v>
       </c>
       <c r="K36" s="6" t="s">
-        <v>117</v>
+        <v>203</v>
       </c>
       <c r="L36" s="6" t="s">
         <v>19</v>
@@ -3957,23 +5385,23 @@
         <v>46081</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>114</v>
+        <v>200</v>
       </c>
       <c r="H37" s="2"/>
       <c r="I37" s="2" t="n">
         <v>38160000</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>111</v>
+        <v>197</v>
       </c>
       <c r="K37" s="6" t="s">
-        <v>117</v>
+        <v>203</v>
       </c>
       <c r="L37" s="6" t="s">
         <v>19</v>
@@ -3999,23 +5427,23 @@
         <v>46081</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>114</v>
+        <v>200</v>
       </c>
       <c r="H38" s="2"/>
       <c r="I38" s="2" t="n">
         <v>38160000</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>111</v>
+        <v>197</v>
       </c>
       <c r="K38" s="6" t="s">
-        <v>117</v>
+        <v>203</v>
       </c>
       <c r="L38" s="6" t="s">
         <v>19</v>
@@ -4041,23 +5469,23 @@
         <v>46081</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>114</v>
+        <v>200</v>
       </c>
       <c r="H39" s="2"/>
       <c r="I39" s="2" t="n">
         <v>62100747</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>116</v>
+        <v>202</v>
       </c>
       <c r="K39" s="6" t="s">
-        <v>117</v>
+        <v>203</v>
       </c>
       <c r="L39" s="6" t="s">
         <v>19</v>
@@ -4083,23 +5511,23 @@
         <v>46081</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>114</v>
+        <v>200</v>
       </c>
       <c r="H40" s="2"/>
       <c r="I40" s="2" t="n">
         <v>62100747</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>116</v>
+        <v>202</v>
       </c>
       <c r="K40" s="6" t="s">
-        <v>117</v>
+        <v>203</v>
       </c>
       <c r="L40" s="6" t="s">
         <v>19</v>
@@ -4125,23 +5553,23 @@
         <v>46081</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>114</v>
+        <v>200</v>
       </c>
       <c r="H41" s="2"/>
       <c r="I41" s="2" t="n">
         <v>62100747</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>116</v>
+        <v>202</v>
       </c>
       <c r="K41" s="6" t="s">
-        <v>117</v>
+        <v>203</v>
       </c>
       <c r="L41" s="6" t="s">
         <v>19</v>
@@ -4167,23 +5595,23 @@
         <v>46081</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>114</v>
+        <v>200</v>
       </c>
       <c r="H42" s="2"/>
       <c r="I42" s="2" t="n">
         <v>62100747</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>116</v>
+        <v>202</v>
       </c>
       <c r="K42" s="6" t="s">
-        <v>117</v>
+        <v>203</v>
       </c>
       <c r="L42" s="6" t="s">
         <v>19</v>
@@ -4209,23 +5637,23 @@
         <v>46081</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>114</v>
+        <v>200</v>
       </c>
       <c r="H43" s="2"/>
       <c r="I43" s="2" t="n">
         <v>62100747</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>116</v>
+        <v>202</v>
       </c>
       <c r="K43" s="6" t="s">
-        <v>117</v>
+        <v>203</v>
       </c>
       <c r="L43" s="6" t="s">
         <v>19</v>
@@ -4251,23 +5679,23 @@
         <v>46081</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>114</v>
+        <v>200</v>
       </c>
       <c r="H44" s="2"/>
       <c r="I44" s="2" t="n">
         <v>62100747</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>116</v>
+        <v>202</v>
       </c>
       <c r="K44" s="6" t="s">
-        <v>117</v>
+        <v>203</v>
       </c>
       <c r="L44" s="6" t="s">
         <v>19</v>
@@ -4293,23 +5721,23 @@
         <v>46081</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>114</v>
+        <v>200</v>
       </c>
       <c r="H45" s="2"/>
       <c r="I45" s="2" t="n">
         <v>62100747</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>116</v>
+        <v>202</v>
       </c>
       <c r="K45" s="6" t="s">
-        <v>117</v>
+        <v>203</v>
       </c>
       <c r="L45" s="6" t="s">
         <v>19</v>
@@ -4335,23 +5763,23 @@
         <v>46081</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>114</v>
+        <v>200</v>
       </c>
       <c r="H46" s="2"/>
       <c r="I46" s="2" t="n">
         <v>62100747</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>116</v>
+        <v>202</v>
       </c>
       <c r="K46" s="6" t="s">
-        <v>117</v>
+        <v>203</v>
       </c>
       <c r="L46" s="6" t="s">
         <v>19</v>
@@ -4377,23 +5805,23 @@
         <v>46081</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>114</v>
+        <v>200</v>
       </c>
       <c r="H47" s="2"/>
       <c r="I47" s="2" t="n">
         <v>62100747</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>116</v>
+        <v>202</v>
       </c>
       <c r="K47" s="6" t="s">
-        <v>117</v>
+        <v>203</v>
       </c>
       <c r="L47" s="6" t="s">
         <v>19</v>
@@ -4419,23 +5847,23 @@
         <v>46081</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>114</v>
+        <v>200</v>
       </c>
       <c r="H48" s="2"/>
       <c r="I48" s="2" t="n">
         <v>62100747</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>116</v>
+        <v>202</v>
       </c>
       <c r="K48" s="6" t="s">
-        <v>117</v>
+        <v>203</v>
       </c>
       <c r="L48" s="6" t="s">
         <v>19</v>
@@ -4461,23 +5889,23 @@
         <v>46081</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>114</v>
+        <v>200</v>
       </c>
       <c r="H49" s="2"/>
       <c r="I49" s="2" t="n">
         <v>62100747</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>116</v>
+        <v>202</v>
       </c>
       <c r="K49" s="6" t="s">
-        <v>117</v>
+        <v>203</v>
       </c>
       <c r="L49" s="6" t="s">
         <v>19</v>
@@ -4503,13 +5931,13 @@
         <v>46112</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>118</v>
+        <v>204</v>
       </c>
       <c r="H50" s="2" t="n">
         <v>120000071</v>
@@ -4518,16 +5946,16 @@
         <v>38160000</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>111</v>
+        <v>197</v>
       </c>
       <c r="K50" s="6" t="s">
-        <v>117</v>
+        <v>203</v>
       </c>
       <c r="L50" s="6" t="s">
         <v>19</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>119</v>
+        <v>205</v>
       </c>
       <c r="N50" s="7" t="n">
         <v>2271351872</v>
@@ -4547,13 +5975,13 @@
         <v>46112</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>118</v>
+        <v>204</v>
       </c>
       <c r="H51" s="2" t="n">
         <v>120000071</v>
@@ -4562,16 +5990,16 @@
         <v>42910311</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>120</v>
+        <v>206</v>
       </c>
       <c r="K51" s="6" t="s">
-        <v>121</v>
+        <v>207</v>
       </c>
       <c r="L51" s="6" t="s">
         <v>19</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>119</v>
+        <v>205</v>
       </c>
       <c r="N51" s="7" t="n">
         <v>80500000</v>
@@ -4591,13 +6019,13 @@
         <v>46112</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>118</v>
+        <v>204</v>
       </c>
       <c r="H52" s="2" t="n">
         <v>120000071</v>
@@ -4606,16 +6034,16 @@
         <v>70051000</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>122</v>
+        <v>208</v>
       </c>
       <c r="K52" s="6" t="s">
-        <v>117</v>
+        <v>203</v>
       </c>
       <c r="L52" s="6" t="s">
         <v>19</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>119</v>
+        <v>205</v>
       </c>
       <c r="N52" s="7" t="n">
         <v>-2271351872</v>
@@ -4635,13 +6063,13 @@
         <v>46112</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G53" s="6" t="s">
-        <v>118</v>
+        <v>204</v>
       </c>
       <c r="H53" s="2" t="n">
         <v>120000071</v>
@@ -4650,16 +6078,16 @@
         <v>70051000</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>122</v>
+        <v>208</v>
       </c>
       <c r="K53" s="6" t="s">
-        <v>121</v>
+        <v>207</v>
       </c>
       <c r="L53" s="6" t="s">
         <v>19</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>119</v>
+        <v>205</v>
       </c>
       <c r="N53" s="7" t="n">
         <v>-80500000</v>
@@ -4679,13 +6107,13 @@
         <v>46112</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F54" s="6" t="s">
-        <v>123</v>
+        <v>209</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>118</v>
+        <v>204</v>
       </c>
       <c r="H54" s="2" t="n">
         <v>120000070</v>
@@ -4694,16 +6122,16 @@
         <v>38160000</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>111</v>
+        <v>197</v>
       </c>
       <c r="K54" s="6" t="s">
-        <v>117</v>
+        <v>203</v>
       </c>
       <c r="L54" s="6" t="s">
         <v>19</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>119</v>
+        <v>205</v>
       </c>
       <c r="N54" s="7" t="n">
         <v>-2271351872</v>
@@ -4723,13 +6151,13 @@
         <v>46112</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F55" s="6" t="s">
-        <v>123</v>
+        <v>209</v>
       </c>
       <c r="G55" s="6" t="s">
-        <v>118</v>
+        <v>204</v>
       </c>
       <c r="H55" s="2" t="n">
         <v>120000070</v>
@@ -4738,16 +6166,16 @@
         <v>42910311</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>120</v>
+        <v>206</v>
       </c>
       <c r="K55" s="6" t="s">
-        <v>121</v>
+        <v>207</v>
       </c>
       <c r="L55" s="6" t="s">
         <v>19</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>119</v>
+        <v>205</v>
       </c>
       <c r="N55" s="7" t="n">
         <v>-80500000</v>
@@ -4767,13 +6195,13 @@
         <v>46112</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F56" s="6" t="s">
-        <v>123</v>
+        <v>209</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>118</v>
+        <v>204</v>
       </c>
       <c r="H56" s="2" t="n">
         <v>120000070</v>
@@ -4782,16 +6210,16 @@
         <v>70051000</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>122</v>
+        <v>208</v>
       </c>
       <c r="K56" s="6" t="s">
-        <v>117</v>
+        <v>203</v>
       </c>
       <c r="L56" s="6" t="s">
         <v>19</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>119</v>
+        <v>205</v>
       </c>
       <c r="N56" s="7" t="n">
         <v>2271351872</v>
@@ -4811,13 +6239,13 @@
         <v>46112</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F57" s="6" t="s">
-        <v>123</v>
+        <v>209</v>
       </c>
       <c r="G57" s="6" t="s">
-        <v>118</v>
+        <v>204</v>
       </c>
       <c r="H57" s="2" t="n">
         <v>120000070</v>
@@ -4826,16 +6254,16 @@
         <v>70051000</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>122</v>
+        <v>208</v>
       </c>
       <c r="K57" s="6" t="s">
-        <v>121</v>
+        <v>207</v>
       </c>
       <c r="L57" s="6" t="s">
         <v>19</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>119</v>
+        <v>205</v>
       </c>
       <c r="N57" s="7" t="n">
         <v>80500000</v>
@@ -4855,23 +6283,23 @@
         <v>46112</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F58" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>114</v>
+        <v>200</v>
       </c>
       <c r="H58" s="2"/>
       <c r="I58" s="2" t="n">
         <v>38160000</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>111</v>
+        <v>197</v>
       </c>
       <c r="K58" s="6" t="s">
-        <v>117</v>
+        <v>203</v>
       </c>
       <c r="L58" s="6" t="s">
         <v>19</v>
@@ -4897,23 +6325,23 @@
         <v>46112</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F59" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G59" s="6" t="s">
-        <v>114</v>
+        <v>200</v>
       </c>
       <c r="H59" s="2"/>
       <c r="I59" s="2" t="n">
         <v>42910311</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>120</v>
+        <v>206</v>
       </c>
       <c r="K59" s="6" t="s">
-        <v>121</v>
+        <v>207</v>
       </c>
       <c r="L59" s="6" t="s">
         <v>19</v>
@@ -4939,23 +6367,23 @@
         <v>46112</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F60" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>114</v>
+        <v>200</v>
       </c>
       <c r="H60" s="2"/>
       <c r="I60" s="2" t="n">
         <v>42910311</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>120</v>
+        <v>206</v>
       </c>
       <c r="K60" s="6" t="s">
-        <v>124</v>
+        <v>210</v>
       </c>
       <c r="L60" s="6" t="s">
         <v>21</v>
@@ -4981,23 +6409,23 @@
         <v>46112</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F61" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G61" s="6" t="s">
-        <v>114</v>
+        <v>200</v>
       </c>
       <c r="H61" s="2"/>
       <c r="I61" s="2" t="n">
         <v>68063200</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>125</v>
+        <v>211</v>
       </c>
       <c r="K61" s="6" t="s">
-        <v>124</v>
+        <v>210</v>
       </c>
       <c r="L61" s="6" t="s">
         <v>21</v>
@@ -5023,23 +6451,23 @@
         <v>46112</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F62" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>114</v>
+        <v>200</v>
       </c>
       <c r="H62" s="2"/>
       <c r="I62" s="2" t="n">
         <v>70051000</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>122</v>
+        <v>208</v>
       </c>
       <c r="K62" s="6" t="s">
-        <v>117</v>
+        <v>203</v>
       </c>
       <c r="L62" s="6" t="s">
         <v>19</v>
@@ -5065,23 +6493,23 @@
         <v>46112</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F63" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G63" s="6" t="s">
-        <v>114</v>
+        <v>200</v>
       </c>
       <c r="H63" s="2"/>
       <c r="I63" s="2" t="n">
         <v>70051000</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>122</v>
+        <v>208</v>
       </c>
       <c r="K63" s="6" t="s">
-        <v>121</v>
+        <v>207</v>
       </c>
       <c r="L63" s="6" t="s">
         <v>19</v>
@@ -5107,23 +6535,23 @@
         <v>46142</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F64" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>126</v>
+        <v>212</v>
       </c>
       <c r="H64" s="2"/>
       <c r="I64" s="2" t="n">
         <v>38160000</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>111</v>
+        <v>197</v>
       </c>
       <c r="K64" s="6" t="s">
-        <v>127</v>
+        <v>213</v>
       </c>
       <c r="L64" s="6" t="s">
         <v>23</v>
@@ -5149,23 +6577,23 @@
         <v>46142</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F65" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G65" s="6" t="s">
-        <v>126</v>
+        <v>212</v>
       </c>
       <c r="H65" s="2"/>
       <c r="I65" s="2" t="n">
         <v>38160000</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>111</v>
+        <v>197</v>
       </c>
       <c r="K65" s="6" t="s">
-        <v>128</v>
+        <v>214</v>
       </c>
       <c r="L65" s="6" t="s">
         <v>25</v>
@@ -5191,23 +6619,23 @@
         <v>46142</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F66" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>126</v>
+        <v>212</v>
       </c>
       <c r="H66" s="2"/>
       <c r="I66" s="2" t="n">
         <v>38160000</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>111</v>
+        <v>197</v>
       </c>
       <c r="K66" s="6" t="s">
-        <v>129</v>
+        <v>215</v>
       </c>
       <c r="L66" s="6" t="s">
         <v>26</v>
@@ -5233,23 +6661,23 @@
         <v>46142</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F67" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G67" s="6" t="s">
-        <v>126</v>
+        <v>212</v>
       </c>
       <c r="H67" s="2"/>
       <c r="I67" s="2" t="n">
         <v>42910311</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>120</v>
+        <v>206</v>
       </c>
       <c r="K67" s="6" t="s">
-        <v>130</v>
+        <v>216</v>
       </c>
       <c r="L67" s="6" t="s">
         <v>23</v>
@@ -5275,23 +6703,23 @@
         <v>46142</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F68" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>126</v>
+        <v>212</v>
       </c>
       <c r="H68" s="2"/>
       <c r="I68" s="2" t="n">
         <v>42910311</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>120</v>
+        <v>206</v>
       </c>
       <c r="K68" s="6" t="s">
-        <v>131</v>
+        <v>217</v>
       </c>
       <c r="L68" s="6" t="s">
         <v>25</v>
@@ -5317,23 +6745,23 @@
         <v>46142</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F69" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G69" s="6" t="s">
-        <v>126</v>
+        <v>212</v>
       </c>
       <c r="H69" s="2"/>
       <c r="I69" s="2" t="n">
         <v>42910311</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>120</v>
+        <v>206</v>
       </c>
       <c r="K69" s="6" t="s">
-        <v>132</v>
+        <v>218</v>
       </c>
       <c r="L69" s="6" t="s">
         <v>26</v>
@@ -5359,23 +6787,23 @@
         <v>46142</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F70" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>126</v>
+        <v>212</v>
       </c>
       <c r="H70" s="2"/>
       <c r="I70" s="2" t="n">
         <v>70051000</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>122</v>
+        <v>208</v>
       </c>
       <c r="K70" s="6" t="s">
-        <v>127</v>
+        <v>213</v>
       </c>
       <c r="L70" s="6" t="s">
         <v>23</v>
@@ -5401,23 +6829,23 @@
         <v>46142</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F71" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G71" s="6" t="s">
-        <v>126</v>
+        <v>212</v>
       </c>
       <c r="H71" s="2"/>
       <c r="I71" s="2" t="n">
         <v>70051000</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>122</v>
+        <v>208</v>
       </c>
       <c r="K71" s="6" t="s">
-        <v>130</v>
+        <v>216</v>
       </c>
       <c r="L71" s="6" t="s">
         <v>23</v>
@@ -5443,23 +6871,23 @@
         <v>46142</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F72" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>126</v>
+        <v>212</v>
       </c>
       <c r="H72" s="2"/>
       <c r="I72" s="2" t="n">
         <v>70051000</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>122</v>
+        <v>208</v>
       </c>
       <c r="K72" s="6" t="s">
-        <v>128</v>
+        <v>214</v>
       </c>
       <c r="L72" s="6" t="s">
         <v>25</v>
@@ -5485,23 +6913,23 @@
         <v>46142</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F73" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G73" s="6" t="s">
-        <v>126</v>
+        <v>212</v>
       </c>
       <c r="H73" s="2"/>
       <c r="I73" s="2" t="n">
         <v>70051000</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>122</v>
+        <v>208</v>
       </c>
       <c r="K73" s="6" t="s">
-        <v>131</v>
+        <v>217</v>
       </c>
       <c r="L73" s="6" t="s">
         <v>25</v>
@@ -5527,23 +6955,23 @@
         <v>46142</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F74" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>126</v>
+        <v>212</v>
       </c>
       <c r="H74" s="2"/>
       <c r="I74" s="2" t="n">
         <v>70051000</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>122</v>
+        <v>208</v>
       </c>
       <c r="K74" s="6" t="s">
-        <v>129</v>
+        <v>215</v>
       </c>
       <c r="L74" s="6" t="s">
         <v>26</v>
@@ -5569,23 +6997,23 @@
         <v>46142</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F75" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G75" s="6" t="s">
-        <v>126</v>
+        <v>212</v>
       </c>
       <c r="H75" s="2"/>
       <c r="I75" s="2" t="n">
         <v>70051000</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>122</v>
+        <v>208</v>
       </c>
       <c r="K75" s="6" t="s">
-        <v>132</v>
+        <v>218</v>
       </c>
       <c r="L75" s="6" t="s">
         <v>26</v>
@@ -5611,23 +7039,23 @@
         <v>46142</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F76" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>133</v>
+        <v>219</v>
       </c>
       <c r="H76" s="2"/>
       <c r="I76" s="2" t="n">
         <v>38160000</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>111</v>
+        <v>197</v>
       </c>
       <c r="K76" s="6" t="s">
-        <v>134</v>
+        <v>220</v>
       </c>
       <c r="L76" s="6" t="s">
         <v>19</v>
@@ -5653,23 +7081,23 @@
         <v>46142</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F77" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G77" s="6" t="s">
-        <v>133</v>
+        <v>219</v>
       </c>
       <c r="H77" s="2"/>
       <c r="I77" s="2" t="n">
         <v>42910311</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>120</v>
+        <v>206</v>
       </c>
       <c r="K77" s="6" t="s">
-        <v>135</v>
+        <v>221</v>
       </c>
       <c r="L77" s="6" t="s">
         <v>19</v>
@@ -5695,23 +7123,23 @@
         <v>46142</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F78" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>133</v>
+        <v>219</v>
       </c>
       <c r="H78" s="2"/>
       <c r="I78" s="2" t="n">
         <v>62100747</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>116</v>
+        <v>202</v>
       </c>
       <c r="K78" s="6" t="s">
-        <v>134</v>
+        <v>220</v>
       </c>
       <c r="L78" s="6" t="s">
         <v>19</v>
@@ -5737,23 +7165,23 @@
         <v>46142</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F79" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G79" s="6" t="s">
-        <v>133</v>
+        <v>219</v>
       </c>
       <c r="H79" s="2"/>
       <c r="I79" s="2" t="n">
         <v>68063200</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>125</v>
+        <v>211</v>
       </c>
       <c r="K79" s="6" t="s">
-        <v>135</v>
+        <v>221</v>
       </c>
       <c r="L79" s="6" t="s">
         <v>19</v>
@@ -5779,23 +7207,23 @@
         <v>46142</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F80" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>133</v>
+        <v>219</v>
       </c>
       <c r="H80" s="2"/>
       <c r="I80" s="2" t="n">
         <v>68063200</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>125</v>
+        <v>211</v>
       </c>
       <c r="K80" s="6" t="s">
-        <v>135</v>
+        <v>221</v>
       </c>
       <c r="L80" s="6" t="s">
         <v>19</v>
@@ -5821,23 +7249,23 @@
         <v>46142</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F81" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G81" s="6" t="s">
-        <v>133</v>
+        <v>219</v>
       </c>
       <c r="H81" s="2"/>
       <c r="I81" s="2" t="n">
         <v>68063200</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>125</v>
+        <v>211</v>
       </c>
       <c r="K81" s="6" t="s">
-        <v>135</v>
+        <v>221</v>
       </c>
       <c r="L81" s="6" t="s">
         <v>19</v>
@@ -5863,23 +7291,23 @@
         <v>46173</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F82" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>126</v>
+        <v>212</v>
       </c>
       <c r="H82" s="2"/>
       <c r="I82" s="2" t="n">
         <v>38160000</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>111</v>
+        <v>197</v>
       </c>
       <c r="K82" s="6" t="s">
-        <v>136</v>
+        <v>222</v>
       </c>
       <c r="L82" s="6" t="s">
         <v>28</v>
@@ -5905,23 +7333,23 @@
         <v>46173</v>
       </c>
       <c r="E83" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F83" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G83" s="6" t="s">
-        <v>126</v>
+        <v>212</v>
       </c>
       <c r="H83" s="2"/>
       <c r="I83" s="2" t="n">
         <v>38160000</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>111</v>
+        <v>197</v>
       </c>
       <c r="K83" s="6" t="s">
-        <v>137</v>
+        <v>223</v>
       </c>
       <c r="L83" s="6" t="s">
         <v>29</v>
@@ -5947,23 +7375,23 @@
         <v>46173</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F84" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>126</v>
+        <v>212</v>
       </c>
       <c r="H84" s="2"/>
       <c r="I84" s="2" t="n">
         <v>42910311</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>120</v>
+        <v>206</v>
       </c>
       <c r="K84" s="6" t="s">
-        <v>138</v>
+        <v>224</v>
       </c>
       <c r="L84" s="6" t="s">
         <v>28</v>
@@ -5989,23 +7417,23 @@
         <v>46173</v>
       </c>
       <c r="E85" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F85" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G85" s="6" t="s">
-        <v>126</v>
+        <v>212</v>
       </c>
       <c r="H85" s="2"/>
       <c r="I85" s="2" t="n">
         <v>42910311</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>120</v>
+        <v>206</v>
       </c>
       <c r="K85" s="6" t="s">
-        <v>139</v>
+        <v>225</v>
       </c>
       <c r="L85" s="6" t="s">
         <v>29</v>
@@ -6031,23 +7459,23 @@
         <v>46173</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F86" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>126</v>
+        <v>212</v>
       </c>
       <c r="H86" s="2"/>
       <c r="I86" s="2" t="n">
         <v>70051000</v>
       </c>
       <c r="J86" s="2" t="s">
-        <v>122</v>
+        <v>208</v>
       </c>
       <c r="K86" s="6" t="s">
-        <v>136</v>
+        <v>222</v>
       </c>
       <c r="L86" s="6" t="s">
         <v>28</v>
@@ -6073,23 +7501,23 @@
         <v>46173</v>
       </c>
       <c r="E87" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F87" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G87" s="6" t="s">
-        <v>126</v>
+        <v>212</v>
       </c>
       <c r="H87" s="2"/>
       <c r="I87" s="2" t="n">
         <v>70051000</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>122</v>
+        <v>208</v>
       </c>
       <c r="K87" s="6" t="s">
-        <v>138</v>
+        <v>224</v>
       </c>
       <c r="L87" s="6" t="s">
         <v>28</v>
@@ -6115,23 +7543,23 @@
         <v>46173</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F88" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>126</v>
+        <v>212</v>
       </c>
       <c r="H88" s="2"/>
       <c r="I88" s="2" t="n">
         <v>70051000</v>
       </c>
       <c r="J88" s="2" t="s">
-        <v>122</v>
+        <v>208</v>
       </c>
       <c r="K88" s="6" t="s">
-        <v>137</v>
+        <v>223</v>
       </c>
       <c r="L88" s="6" t="s">
         <v>29</v>
@@ -6157,23 +7585,23 @@
         <v>46173</v>
       </c>
       <c r="E89" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F89" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G89" s="6" t="s">
-        <v>126</v>
+        <v>212</v>
       </c>
       <c r="H89" s="2"/>
       <c r="I89" s="2" t="n">
         <v>70051000</v>
       </c>
       <c r="J89" s="2" t="s">
-        <v>122</v>
+        <v>208</v>
       </c>
       <c r="K89" s="6" t="s">
-        <v>139</v>
+        <v>225</v>
       </c>
       <c r="L89" s="6" t="s">
         <v>29</v>
@@ -6199,23 +7627,23 @@
         <v>46203</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F90" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>126</v>
+        <v>212</v>
       </c>
       <c r="H90" s="2"/>
       <c r="I90" s="2" t="n">
         <v>42910311</v>
       </c>
       <c r="J90" s="2" t="s">
-        <v>120</v>
+        <v>206</v>
       </c>
       <c r="K90" s="6" t="s">
-        <v>140</v>
+        <v>226</v>
       </c>
       <c r="L90" s="6" t="s">
         <v>19</v>
@@ -6241,23 +7669,23 @@
         <v>46203</v>
       </c>
       <c r="E91" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F91" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G91" s="6" t="s">
-        <v>126</v>
+        <v>212</v>
       </c>
       <c r="H91" s="2"/>
       <c r="I91" s="2" t="n">
         <v>42910311</v>
       </c>
       <c r="J91" s="2" t="s">
-        <v>120</v>
+        <v>206</v>
       </c>
       <c r="K91" s="6" t="s">
-        <v>141</v>
+        <v>227</v>
       </c>
       <c r="L91" s="6" t="s">
         <v>19</v>
@@ -6283,23 +7711,23 @@
         <v>46203</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F92" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>126</v>
+        <v>212</v>
       </c>
       <c r="H92" s="2"/>
       <c r="I92" s="2" t="n">
         <v>68063200</v>
       </c>
       <c r="J92" s="2" t="s">
-        <v>125</v>
+        <v>211</v>
       </c>
       <c r="K92" s="6" t="s">
-        <v>140</v>
+        <v>226</v>
       </c>
       <c r="L92" s="6" t="s">
         <v>19</v>
@@ -6325,23 +7753,23 @@
         <v>46203</v>
       </c>
       <c r="E93" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F93" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G93" s="6" t="s">
-        <v>126</v>
+        <v>212</v>
       </c>
       <c r="H93" s="2"/>
       <c r="I93" s="2" t="n">
         <v>70051000</v>
       </c>
       <c r="J93" s="2" t="s">
-        <v>122</v>
+        <v>208</v>
       </c>
       <c r="K93" s="6" t="s">
-        <v>141</v>
+        <v>227</v>
       </c>
       <c r="L93" s="6" t="s">
         <v>19</v>
@@ -6367,23 +7795,23 @@
         <v>46234</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F94" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>114</v>
+        <v>200</v>
       </c>
       <c r="H94" s="2"/>
       <c r="I94" s="2" t="n">
         <v>38160000</v>
       </c>
       <c r="J94" s="2" t="s">
-        <v>111</v>
+        <v>197</v>
       </c>
       <c r="K94" s="6" t="s">
-        <v>134</v>
+        <v>220</v>
       </c>
       <c r="L94" s="6" t="s">
         <v>19</v>
@@ -6409,23 +7837,23 @@
         <v>46234</v>
       </c>
       <c r="E95" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F95" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G95" s="6" t="s">
-        <v>114</v>
+        <v>200</v>
       </c>
       <c r="H95" s="2"/>
       <c r="I95" s="2" t="n">
         <v>62100747</v>
       </c>
       <c r="J95" s="2" t="s">
-        <v>116</v>
+        <v>202</v>
       </c>
       <c r="K95" s="6" t="s">
-        <v>134</v>
+        <v>220</v>
       </c>
       <c r="L95" s="6" t="s">
         <v>19</v>
@@ -6451,23 +7879,23 @@
         <v>46295</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F96" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>142</v>
+        <v>228</v>
       </c>
       <c r="H96" s="2"/>
       <c r="I96" s="2" t="n">
         <v>38160000</v>
       </c>
       <c r="J96" s="2" t="s">
-        <v>111</v>
+        <v>197</v>
       </c>
       <c r="K96" s="6" t="s">
-        <v>143</v>
+        <v>229</v>
       </c>
       <c r="L96" s="6" t="s">
         <v>23</v>
@@ -6493,23 +7921,23 @@
         <v>46295</v>
       </c>
       <c r="E97" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F97" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G97" s="6" t="s">
-        <v>142</v>
+        <v>228</v>
       </c>
       <c r="H97" s="2"/>
       <c r="I97" s="2" t="n">
         <v>42910311</v>
       </c>
       <c r="J97" s="2" t="s">
-        <v>120</v>
+        <v>206</v>
       </c>
       <c r="K97" s="6" t="s">
-        <v>144</v>
+        <v>230</v>
       </c>
       <c r="L97" s="6" t="s">
         <v>23</v>
@@ -6535,23 +7963,23 @@
         <v>46295</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F98" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>142</v>
+        <v>228</v>
       </c>
       <c r="H98" s="2"/>
       <c r="I98" s="2" t="n">
         <v>42910311</v>
       </c>
       <c r="J98" s="2" t="s">
-        <v>120</v>
+        <v>206</v>
       </c>
       <c r="K98" s="6" t="s">
-        <v>141</v>
+        <v>227</v>
       </c>
       <c r="L98" s="6" t="s">
         <v>19</v>
@@ -6577,23 +8005,23 @@
         <v>46295</v>
       </c>
       <c r="E99" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F99" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G99" s="6" t="s">
-        <v>142</v>
+        <v>228</v>
       </c>
       <c r="H99" s="2"/>
       <c r="I99" s="2" t="n">
         <v>70051000</v>
       </c>
       <c r="J99" s="2" t="s">
-        <v>122</v>
+        <v>208</v>
       </c>
       <c r="K99" s="6" t="s">
-        <v>145</v>
+        <v>231</v>
       </c>
       <c r="L99" s="6" t="s">
         <v>23</v>
@@ -6619,23 +8047,23 @@
         <v>46295</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F100" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>142</v>
+        <v>228</v>
       </c>
       <c r="H100" s="2"/>
       <c r="I100" s="2" t="n">
         <v>70051000</v>
       </c>
       <c r="J100" s="2" t="s">
-        <v>122</v>
+        <v>208</v>
       </c>
       <c r="K100" s="6" t="s">
-        <v>144</v>
+        <v>230</v>
       </c>
       <c r="L100" s="6" t="s">
         <v>23</v>
@@ -6661,23 +8089,23 @@
         <v>46295</v>
       </c>
       <c r="E101" s="6" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="F101" s="6" t="s">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="G101" s="6" t="s">
-        <v>142</v>
+        <v>228</v>
       </c>
       <c r="H101" s="2"/>
       <c r="I101" s="2" t="n">
         <v>70051000</v>
       </c>
       <c r="J101" s="2" t="s">
-        <v>122</v>
+        <v>208</v>
       </c>
       <c r="K101" s="6" t="s">
-        <v>141</v>
+        <v>227</v>
       </c>
       <c r="L101" s="6" t="s">
         <v>19</v>
@@ -6702,7 +8130,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -6722,28 +8150,28 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="18" t="s">
-        <v>96</v>
+        <v>182</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>97</v>
+        <v>183</v>
       </c>
       <c r="C1" s="18" t="s">
-        <v>98</v>
+        <v>184</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>100</v>
+        <v>186</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>102</v>
+        <v>188</v>
       </c>
       <c r="F1" s="18" t="s">
-        <v>106</v>
+        <v>192</v>
       </c>
       <c r="G1" s="18" t="s">
-        <v>146</v>
+        <v>232</v>
       </c>
       <c r="H1" s="18" t="s">
-        <v>147</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6757,16 +8185,16 @@
         <v>46031</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>148</v>
+        <v>234</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>149</v>
+        <v>235</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>150</v>
+        <v>236</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>151</v>
+        <v>237</v>
       </c>
       <c r="H2" s="7" t="n">
         <v>669656093</v>
@@ -6783,16 +8211,16 @@
         <v>46031</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>148</v>
+        <v>234</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>149</v>
+        <v>235</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>150</v>
+        <v>236</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>151</v>
+        <v>237</v>
       </c>
       <c r="H3" s="7" t="n">
         <v>201128684</v>
@@ -6809,16 +8237,16 @@
         <v>46031</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>148</v>
+        <v>234</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>149</v>
+        <v>235</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>150</v>
+        <v>236</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>151</v>
+        <v>237</v>
       </c>
       <c r="H4" s="7" t="n">
         <v>1355026284</v>
@@ -6835,16 +8263,16 @@
         <v>46031</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>148</v>
+        <v>234</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>149</v>
+        <v>235</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>150</v>
+        <v>236</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>151</v>
+        <v>237</v>
       </c>
       <c r="H5" s="7" t="n">
         <v>139366409</v>
@@ -6861,16 +8289,16 @@
         <v>46031</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>148</v>
+        <v>234</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>149</v>
+        <v>235</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>150</v>
+        <v>236</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>151</v>
+        <v>237</v>
       </c>
       <c r="H6" s="7" t="n">
         <v>732377864</v>
@@ -6887,16 +8315,16 @@
         <v>46031</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>148</v>
+        <v>234</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>149</v>
+        <v>235</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>150</v>
+        <v>236</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>151</v>
+        <v>237</v>
       </c>
       <c r="H7" s="7" t="n">
         <v>637997113</v>
@@ -6913,16 +8341,16 @@
         <v>46034</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>152</v>
+        <v>238</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>153</v>
+        <v>239</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>154</v>
+        <v>240</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>155</v>
+        <v>241</v>
       </c>
       <c r="H8" s="7" t="n">
         <v>194099242</v>
@@ -6939,16 +8367,16 @@
         <v>46034</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>152</v>
+        <v>238</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>153</v>
+        <v>239</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>154</v>
+        <v>240</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>155</v>
+        <v>241</v>
       </c>
       <c r="H9" s="7" t="n">
         <v>1313212538</v>
@@ -6965,16 +8393,16 @@
         <v>46034</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>152</v>
+        <v>238</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>153</v>
+        <v>239</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>154</v>
+        <v>240</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>155</v>
+        <v>241</v>
       </c>
       <c r="H10" s="7" t="n">
         <v>292240228</v>
@@ -6991,16 +8419,16 @@
         <v>46034</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>152</v>
+        <v>238</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>153</v>
+        <v>239</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>154</v>
+        <v>240</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>155</v>
+        <v>241</v>
       </c>
       <c r="H11" s="7" t="n">
         <v>240492525</v>
@@ -7017,16 +8445,16 @@
         <v>46034</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>152</v>
+        <v>238</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>153</v>
+        <v>239</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>154</v>
+        <v>240</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>155</v>
+        <v>241</v>
       </c>
       <c r="H12" s="7" t="n">
         <v>1851555922</v>
@@ -7043,16 +8471,16 @@
         <v>46034</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>152</v>
+        <v>238</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>153</v>
+        <v>239</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>154</v>
+        <v>240</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>155</v>
+        <v>241</v>
       </c>
       <c r="H13" s="7" t="n">
         <v>767113411</v>
@@ -7069,16 +8497,16 @@
         <v>46034</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>152</v>
+        <v>238</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>153</v>
+        <v>239</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>154</v>
+        <v>240</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>155</v>
+        <v>241</v>
       </c>
       <c r="H14" s="7" t="n">
         <v>632116008</v>
@@ -7095,16 +8523,16 @@
         <v>46058</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>152</v>
+        <v>238</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>156</v>
+        <v>242</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>154</v>
+        <v>240</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>155</v>
+        <v>241</v>
       </c>
       <c r="H15" s="7" t="n">
         <v>773240036</v>
@@ -7121,16 +8549,16 @@
         <v>46140</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>157</v>
+        <v>243</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>158</v>
+        <v>244</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>150</v>
+        <v>236</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>159</v>
+        <v>245</v>
       </c>
       <c r="H16" s="7" t="n">
         <v>-554771272</v>
@@ -7147,16 +8575,16 @@
         <v>46140</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>148</v>
+        <v>234</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>158</v>
+        <v>244</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>150</v>
+        <v>236</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>159</v>
+        <v>245</v>
       </c>
       <c r="H17" s="7" t="n">
         <v>554771272</v>
@@ -7173,16 +8601,16 @@
         <v>46140</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>148</v>
+        <v>234</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>158</v>
+        <v>244</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>150</v>
+        <v>236</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>159</v>
+        <v>245</v>
       </c>
       <c r="H18" s="7" t="n">
         <v>554771272</v>
@@ -7199,16 +8627,16 @@
         <v>46212</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>152</v>
+        <v>238</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>160</v>
+        <v>246</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>154</v>
+        <v>240</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>161</v>
+        <v>247</v>
       </c>
       <c r="H19" s="7" t="n">
         <v>742500000</v>
@@ -7225,7 +8653,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>162</v>
+        <v>248</v>
       </c>
     </row>
   </sheetData>
